--- a/여행예산_상하이반영.xlsx
+++ b/여행예산_상하이반영.xlsx
@@ -3471,7 +3471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="37" min="1" max="1"/>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="C19" s="68" t="inlineStr">
         <is>
-          <t>아테네 — 종일 관광</t>
+          <t>아테네 — 종일 관광 (숙소 30유로 확정)</t>
         </is>
       </c>
       <c r="D19" s="54">
@@ -4223,7 +4223,7 @@
         <v>45000</v>
       </c>
       <c r="F19" s="54" t="n">
-        <v>90000</v>
+        <v>49200</v>
       </c>
       <c r="G19" s="54" t="n">
         <v>8000</v>
@@ -4463,12 +4463,19 @@
     <row r="34">
       <c r="A34" s="37" t="inlineStr">
         <is>
-          <t>※ 아부다비 숙소는 TRYP by Wyndham Abu Dhabi City Center(칼리파 bin 자이드 St) — 항공권 스톱오버에 포함되어 숙박비 0원. A2 공항버스가 이 도로에 정차합니다.</t>
+          <t>※ 아테네 숙소는 30유로/1박 확정 — 신타그마 근처. 원래 잡아둔 90,000원에서 40,800원 줄었습니다. 08:00 짐 보관이 가능한 곳이어야 합니다(아크로폴리스 큰 가방 반입 불가).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="37" t="inlineStr">
+        <is>
+          <t>※ 아부다비 숙소는 TRYP by Wyndham Abu Dhabi City Center(칼리파 bin 자이드 St) — 항공권 스톱오버에 포함되어 숙박비 0원. A2 공항버스가 이 도로에 정차합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>※ 9/24 주타는 대중교통이 없어 4WD 택시 왕복 80라리(1인 전액)입니다. 카즈베기 게스트하우스에서 동행을 구하면 40라리로 줄어듭니다.</t>
         </is>

--- a/여행예산_상하이반영.xlsx
+++ b/여행예산_상하이반영.xlsx
@@ -948,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="37" min="1" max="1"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="B19" s="41" t="inlineStr">
         <is>
-          <t>알라베르디 → 예레반</t>
+          <t>알라베르디 → 바나조르</t>
         </is>
       </c>
       <c r="C19" s="41" t="inlineStr">
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="E19" s="54" t="n">
-        <v>1900</v>
+        <v>500</v>
       </c>
       <c r="F19" s="45" t="inlineStr">
         <is>
@@ -1679,19 +1679,19 @@
       </c>
       <c r="I19" s="47" t="inlineStr">
         <is>
-          <t>첫차 07:30 · 스피타크·아파란 경유 약 4시간 · 직행 없으면 바나조르 환승</t>
+          <t>1시간 · 09:00·10:30·11:00·13:00 네 편</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="38">
       <c r="A20" s="45" t="inlineStr">
         <is>
-          <t>10/2</t>
+          <t>9/27</t>
         </is>
       </c>
       <c r="B20" s="41" t="inlineStr">
         <is>
-          <t>예레반 → 세반 왕복</t>
+          <t>바나조르 → 귬리</t>
         </is>
       </c>
       <c r="C20" s="41" t="inlineStr">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="E20" s="54" t="n">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="F20" s="45" t="inlineStr">
         <is>
@@ -1723,33 +1723,33 @@
       </c>
       <c r="I20" s="47" t="inlineStr">
         <is>
-          <t>편도 1,000~1,500드람 · 편도 1~1.5시간</t>
+          <t>스피타크 경유 1시간 40분 · 1,000~1,500드람</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="38">
       <c r="A21" s="45" t="inlineStr">
         <is>
-          <t>10/2</t>
+          <t>9/28</t>
         </is>
       </c>
       <c r="B21" s="41" t="inlineStr">
         <is>
-          <t>세반 → 세바나방크 반도</t>
+          <t>귬리 → 예레반</t>
         </is>
       </c>
       <c r="C21" s="41" t="inlineStr">
         <is>
-          <t>도보 또는 택시</t>
+          <t>마르슈르트카</t>
         </is>
       </c>
       <c r="D21" s="53" t="inlineStr">
         <is>
-          <t>시내</t>
+          <t>시외</t>
         </is>
       </c>
       <c r="E21" s="54" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F21" s="45" t="inlineStr">
         <is>
@@ -1762,38 +1762,38 @@
       </c>
       <c r="H21" s="55" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>○</t>
         </is>
       </c>
       <c r="I21" s="47" t="inlineStr">
         <is>
-          <t>도보 30분 · 1인 단독이라 전액 부담</t>
+          <t>2시간 · 수시 출발 · 급행 전동열차도 비슷한 값</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="38">
       <c r="A22" s="45" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>10/2</t>
         </is>
       </c>
       <c r="B22" s="41" t="inlineStr">
         <is>
-          <t>킬리키아 터미널 → 시내</t>
+          <t>예레반 → 세반 왕복</t>
         </is>
       </c>
       <c r="C22" s="41" t="inlineStr">
         <is>
-          <t>버스</t>
+          <t>마르슈르트카</t>
         </is>
       </c>
       <c r="D22" s="53" t="inlineStr">
         <is>
-          <t>시내</t>
+          <t>시외</t>
         </is>
       </c>
       <c r="E22" s="54" t="n">
-        <v>100</v>
+        <v>2500</v>
       </c>
       <c r="F22" s="45" t="inlineStr">
         <is>
@@ -1811,24 +1811,24 @@
       </c>
       <c r="I22" s="47" t="inlineStr">
         <is>
-          <t>또는 얀덱스 택시</t>
+          <t>편도 1,000~1,500드람 · 편도 1~1.5시간</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="38">
       <c r="A23" s="45" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/2</t>
         </is>
       </c>
       <c r="B23" s="41" t="inlineStr">
         <is>
-          <t>가르니 → 게하르트 왕복</t>
+          <t>세반 → 세바나방크 반도</t>
         </is>
       </c>
       <c r="C23" s="41" t="inlineStr">
         <is>
-          <t>택시</t>
+          <t>도보 또는 택시</t>
         </is>
       </c>
       <c r="D23" s="53" t="inlineStr">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="E23" s="54" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="F23" s="45" t="inlineStr">
         <is>
@@ -1850,29 +1850,29 @@
       </c>
       <c r="H23" s="55" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>△</t>
         </is>
       </c>
       <c r="I23" s="43" t="inlineStr">
         <is>
-          <t>9km, 대중교통 없음 · 1인 단독이라 전액 부담</t>
+          <t>도보 30분 · 1인 단독이라 전액 부담</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="38">
       <c r="A24" s="45" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>9/27</t>
         </is>
       </c>
       <c r="B24" s="41" t="inlineStr">
         <is>
-          <t>예레반 → 에치미아진 왕복</t>
+          <t>킬리키아 터미널 → 시내</t>
         </is>
       </c>
       <c r="C24" s="41" t="inlineStr">
         <is>
-          <t>마르슈르트카</t>
+          <t>버스</t>
         </is>
       </c>
       <c r="D24" s="53" t="inlineStr">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="E24" s="54" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F24" s="45" t="inlineStr">
         <is>
@@ -1899,24 +1899,24 @@
       </c>
       <c r="I24" s="47" t="inlineStr">
         <is>
-          <t>킬리키아 터미널</t>
+          <t>또는 얀덱스 택시</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="38">
       <c r="A25" s="45" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>9/30</t>
         </is>
       </c>
       <c r="B25" s="41" t="inlineStr">
         <is>
-          <t>예레반 → 코르 비랍 왕복</t>
+          <t>가르니 → 게하르트 왕복</t>
         </is>
       </c>
       <c r="C25" s="41" t="inlineStr">
         <is>
-          <t>마르슈르트카</t>
+          <t>택시</t>
         </is>
       </c>
       <c r="D25" s="53" t="inlineStr">
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="E25" s="54" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="F25" s="45" t="inlineStr">
         <is>
@@ -1938,24 +1938,24 @@
       </c>
       <c r="H25" s="55" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="I25" s="47" t="inlineStr">
         <is>
-          <t>하루 몇 편뿐</t>
+          <t>9km, 대중교통 없음 · 1인 단독이라 전액 부담</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="38">
       <c r="A26" s="45" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/1</t>
         </is>
       </c>
       <c r="B26" s="41" t="inlineStr">
         <is>
-          <t>예레반 → 아레니 갈림길 → 고리스</t>
+          <t>예레반 → 에치미아진 왕복</t>
         </is>
       </c>
       <c r="C26" s="41" t="inlineStr">
@@ -1965,11 +1965,11 @@
       </c>
       <c r="D26" s="53" t="inlineStr">
         <is>
-          <t>시외</t>
+          <t>시내</t>
         </is>
       </c>
       <c r="E26" s="54" t="n">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="F26" s="45" t="inlineStr">
         <is>
@@ -1987,24 +1987,24 @@
       </c>
       <c r="I26" s="47" t="inlineStr">
         <is>
-          <t>노라방크 입구에서 하차 후 지나가는 차 재탑승</t>
+          <t>킬리키아 터미널</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="38">
       <c r="A27" s="45" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>9/29</t>
         </is>
       </c>
       <c r="B27" s="41" t="inlineStr">
         <is>
-          <t>아레니 갈림길 → 노라방크 왕복</t>
+          <t>예레반 → 코르 비랍 왕복</t>
         </is>
       </c>
       <c r="C27" s="41" t="inlineStr">
         <is>
-          <t>택시</t>
+          <t>마르슈르트카</t>
         </is>
       </c>
       <c r="D27" s="53" t="inlineStr">
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="E27" s="54" t="n">
-        <v>4000</v>
+        <v>1200</v>
       </c>
       <c r="F27" s="45" t="inlineStr">
         <is>
@@ -2026,24 +2026,24 @@
       </c>
       <c r="H27" s="55" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>△</t>
         </is>
       </c>
       <c r="I27" s="43" t="inlineStr">
         <is>
-          <t>8km, 대중교통 없음 · 1인 단독이라 전액 부담</t>
+          <t>하루 몇 편뿐</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="38">
       <c r="A28" s="45" t="inlineStr">
         <is>
-          <t>10/1</t>
+          <t>10/3</t>
         </is>
       </c>
       <c r="B28" s="41" t="inlineStr">
         <is>
-          <t>고리스 → 할리조르 승강장 왕복</t>
+          <t>예레반 → 즈바르트노츠 공항</t>
         </is>
       </c>
       <c r="C28" s="41" t="inlineStr">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="E28" s="54" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="F28" s="45" t="inlineStr">
         <is>
@@ -2070,46 +2070,46 @@
       </c>
       <c r="H28" s="55" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>△</t>
         </is>
       </c>
       <c r="I28" s="47" t="inlineStr">
         <is>
-          <t>타테브 케이블카 승강장 · 1인 단독이라 전액 부담</t>
+          <t>01:30경 출발, 심야 할증 감안</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="38">
       <c r="A29" s="45" t="inlineStr">
         <is>
-          <t>10/1</t>
+          <t>10/3</t>
         </is>
       </c>
       <c r="B29" s="41" t="inlineStr">
         <is>
-          <t>고리스 → 예레반</t>
+          <t>아테네 공항 → 신타그마역</t>
         </is>
       </c>
       <c r="C29" s="41" t="inlineStr">
         <is>
-          <t>마르슈르트카</t>
+          <t>메트로 3호선</t>
         </is>
       </c>
       <c r="D29" s="53" t="inlineStr">
         <is>
-          <t>시외</t>
+          <t>시내</t>
         </is>
       </c>
       <c r="E29" s="54" t="n">
-        <v>3000</v>
+        <v>10</v>
       </c>
       <c r="F29" s="45" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G29" s="48">
-        <f>ROUND(E29*환율!$B$5/1,0)</f>
+        <f>ROUND(E29*환율!$B$6/1,0)</f>
         <v/>
       </c>
       <c r="H29" s="55" t="inlineStr">
@@ -2119,24 +2119,24 @@
       </c>
       <c r="I29" s="43" t="inlineStr">
         <is>
-          <t>607번 · 고리스 출발 07·09·15·16시 네 편뿐 · 15:00 편 이용 · 4~5시간</t>
+          <t>공항선 정액 10유로, 40분</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="38">
       <c r="A30" s="45" t="inlineStr">
         <is>
-          <t>10/2</t>
+          <t>10/3</t>
         </is>
       </c>
       <c r="B30" s="41" t="inlineStr">
         <is>
-          <t>예레반 시내 (베르니사쥬 등)</t>
+          <t>아테네 시내 이동</t>
         </is>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
-          <t>택시 2회</t>
+          <t>메트로·트램 4~5회</t>
         </is>
       </c>
       <c r="D30" s="53" t="inlineStr">
@@ -2145,42 +2145,42 @@
         </is>
       </c>
       <c r="E30" s="54" t="n">
-        <v>1500</v>
+        <v>6</v>
       </c>
       <c r="F30" s="45" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G30" s="48">
-        <f>ROUND(E30*환율!$B$5/1,0)</f>
+        <f>ROUND(E30*환율!$B$6/1,0)</f>
         <v/>
       </c>
       <c r="H30" s="55" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>○</t>
         </is>
       </c>
       <c r="I30" s="47" t="inlineStr">
         <is>
-          <t>숙소 유지, 짐 이동 없음</t>
+          <t>1회 1.20유로. 대부분 도보권이라 보조 수단</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="38">
       <c r="A31" s="45" t="inlineStr">
         <is>
-          <t>10/3</t>
+          <t>10/4</t>
         </is>
       </c>
       <c r="B31" s="41" t="inlineStr">
         <is>
-          <t>예레반 → 즈바르트노츠 공항</t>
+          <t>아테네 → 공항 (04:10 출발)</t>
         </is>
       </c>
       <c r="C31" s="41" t="inlineStr">
         <is>
-          <t>택시</t>
+          <t>X95 공항버스</t>
         </is>
       </c>
       <c r="D31" s="53" t="inlineStr">
@@ -2189,42 +2189,42 @@
         </is>
       </c>
       <c r="E31" s="54" t="n">
-        <v>4000</v>
+        <v>6.2</v>
       </c>
       <c r="F31" s="45" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G31" s="48">
-        <f>ROUND(E31*환율!$B$5/1,0)</f>
+        <f>ROUND(E31*환율!$B$6/1,0)</f>
         <v/>
       </c>
       <c r="H31" s="55" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>○</t>
         </is>
       </c>
       <c r="I31" s="43" t="inlineStr">
         <is>
-          <t>01:30경 출발, 심야 할증 감안</t>
+          <t>신타그마 발 24시간 운행 · 야간 60분 간격이라 03:55까지 정류장 도착 · 승차권은 전날 지하철역에서 미리 구입 · 택시는 심야 정액 55유로</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="38">
       <c r="A32" s="45" t="inlineStr">
         <is>
-          <t>10/3</t>
+          <t>10/4</t>
         </is>
       </c>
       <c r="B32" s="41" t="inlineStr">
         <is>
-          <t>아테네 공항 → 신타그마역</t>
+          <t>자이드 국제공항 → TRYP 호텔</t>
         </is>
       </c>
       <c r="C32" s="41" t="inlineStr">
         <is>
-          <t>메트로 3호선</t>
+          <t>택시</t>
         </is>
       </c>
       <c r="D32" s="53" t="inlineStr">
@@ -2233,42 +2233,42 @@
         </is>
       </c>
       <c r="E32" s="54" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="F32" s="45" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="G32" s="48">
-        <f>ROUND(E32*환율!$B$6/1,0)</f>
+        <f>ROUND(E32*환율!$B$7/1,0)</f>
         <v/>
       </c>
       <c r="H32" s="55" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="I32" s="47" t="inlineStr">
         <is>
-          <t>공항선 정액 10유로, 40분</t>
+          <t>칼리파 bin 자이드 St · 30~40분 · 미터 약 85~100디르함</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="38">
       <c r="A33" s="45" t="inlineStr">
         <is>
-          <t>10/3</t>
+          <t>10/4</t>
         </is>
       </c>
       <c r="B33" s="41" t="inlineStr">
         <is>
-          <t>아테네 시내 이동</t>
+          <t>TRYP 호텔 → 루브르 아부다비</t>
         </is>
       </c>
       <c r="C33" s="41" t="inlineStr">
         <is>
-          <t>메트로·트램 4~5회</t>
+          <t>택시</t>
         </is>
       </c>
       <c r="D33" s="53" t="inlineStr">
@@ -2277,25 +2277,25 @@
         </is>
       </c>
       <c r="E33" s="54" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="F33" s="45" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="G33" s="48">
-        <f>ROUND(E33*환율!$B$6/1,0)</f>
+        <f>ROUND(E33*환율!$B$7/1,0)</f>
         <v/>
       </c>
       <c r="H33" s="55" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="I33" s="43" t="inlineStr">
         <is>
-          <t>1회 1.20유로. 대부분 도보권이라 보조 수단</t>
+          <t>사디야트 섬 · 약 14km, 20~25분</t>
         </is>
       </c>
     </row>
@@ -2307,12 +2307,12 @@
       </c>
       <c r="B34" s="41" t="inlineStr">
         <is>
-          <t>아테네 → 공항 (04:10 출발)</t>
+          <t>루브르 → 셰이크 자이드 모스크</t>
         </is>
       </c>
       <c r="C34" s="41" t="inlineStr">
         <is>
-          <t>X95 공항버스</t>
+          <t>택시</t>
         </is>
       </c>
       <c r="D34" s="53" t="inlineStr">
@@ -2321,25 +2321,25 @@
         </is>
       </c>
       <c r="E34" s="54" t="n">
-        <v>6.2</v>
+        <v>75</v>
       </c>
       <c r="F34" s="45" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="G34" s="48">
-        <f>ROUND(E34*환율!$B$6/1,0)</f>
+        <f>ROUND(E34*환율!$B$7/1,0)</f>
         <v/>
       </c>
       <c r="H34" s="55" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="I34" s="47" t="inlineStr">
         <is>
-          <t>신타그마 발 24시간 운행 · 야간 60분 간격이라 03:55까지 정류장 도착 · 승차권은 전날 지하철역에서 미리 구입 · 택시는 심야 정액 55유로</t>
+          <t>섬 반대편 횡단 약 28km, 30~35분 · 94번 버스면 2디르함이나 60~75분</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B35" s="41" t="inlineStr">
         <is>
-          <t>자이드 국제공항 → TRYP 호텔</t>
+          <t>모스크 → TRYP 호텔</t>
         </is>
       </c>
       <c r="C35" s="41" t="inlineStr">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="E35" s="54" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="F35" s="45" t="inlineStr">
         <is>
@@ -2383,24 +2383,24 @@
       </c>
       <c r="I35" s="43" t="inlineStr">
         <is>
-          <t>칼리파 bin 자이드 St · 30~40분 · 미터 약 85~100디르함</t>
+          <t>약 14km, 18~20분</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="38">
       <c r="A36" s="45" t="inlineStr">
         <is>
-          <t>10/4</t>
+          <t>10/5</t>
         </is>
       </c>
       <c r="B36" s="41" t="inlineStr">
         <is>
-          <t>TRYP 호텔 → 루브르 아부다비</t>
+          <t>TRYP 호텔 → 공항 (05:30)</t>
         </is>
       </c>
       <c r="C36" s="41" t="inlineStr">
         <is>
-          <t>택시</t>
+          <t>A2 공항버스</t>
         </is>
       </c>
       <c r="D36" s="53" t="inlineStr">
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="E36" s="54" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="F36" s="45" t="inlineStr">
         <is>
@@ -2422,73 +2422,73 @@
       </c>
       <c r="H36" s="55" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>○</t>
         </is>
       </c>
       <c r="I36" s="47" t="inlineStr">
         <is>
-          <t>사디야트 섬 · 약 14km, 20~25분</t>
+          <t>버스 4디르함 + 하필라트 카드 10디르함 · 칼리파 bin 자이드 St 승차 · 40~45분</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="38">
       <c r="A37" s="45" t="inlineStr">
         <is>
-          <t>10/4</t>
+          <t>9/30</t>
         </is>
       </c>
       <c r="B37" s="41" t="inlineStr">
         <is>
-          <t>루브르 → 셰이크 자이드 모스크</t>
+          <t>예레반 → 가르니 왕복</t>
         </is>
       </c>
       <c r="C37" s="41" t="inlineStr">
         <is>
-          <t>택시</t>
+          <t>266·284번 버스</t>
         </is>
       </c>
       <c r="D37" s="53" t="inlineStr">
         <is>
-          <t>시내</t>
+          <t>시외</t>
         </is>
       </c>
       <c r="E37" s="54" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="F37" s="45" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="G37" s="48">
-        <f>ROUND(E37*환율!$B$7/1,0)</f>
+        <f>ROUND(E37*환율!$B$5/1,0)</f>
         <v/>
       </c>
       <c r="H37" s="55" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>○</t>
         </is>
       </c>
       <c r="I37" s="47" t="inlineStr">
         <is>
-          <t>섬 반대편 횡단 약 28km, 30~35분 · 94번 버스면 2디르함이나 60~75분</t>
+          <t>가이 정류장 출발 · 30분 간격 · 왕복 500드람</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="38">
       <c r="A38" s="45" t="inlineStr">
         <is>
-          <t>10/4</t>
+          <t>9/24</t>
         </is>
       </c>
       <c r="B38" s="41" t="inlineStr">
         <is>
-          <t>모스크 → TRYP 호텔</t>
+          <t>스테판츠민다 → 주타 왕복</t>
         </is>
       </c>
       <c r="C38" s="41" t="inlineStr">
         <is>
-          <t>택시</t>
+          <t>4WD 택시 (대기 포함)</t>
         </is>
       </c>
       <c r="D38" s="53" t="inlineStr">
@@ -2497,15 +2497,15 @@
         </is>
       </c>
       <c r="E38" s="54" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="F38" s="45" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="G38" s="48">
-        <f>ROUND(E38*환율!$B$7/1,0)</f>
+        <f>ROUND(E38*환율!$B$4/1,0)</f>
         <v/>
       </c>
       <c r="H38" s="55" t="inlineStr">
@@ -2515,41 +2515,41 @@
       </c>
       <c r="I38" s="47" t="inlineStr">
         <is>
-          <t>약 14km, 18~20분</t>
+          <t>대중교통 없음 · 25km 비포장 · 1인 단독이면 전액. 동행 구하면 40라리</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="38">
       <c r="A39" s="45" t="inlineStr">
         <is>
-          <t>10/5</t>
+          <t>9/25</t>
         </is>
       </c>
       <c r="B39" s="41" t="inlineStr">
         <is>
-          <t>TRYP 호텔 → 공항 (05:30)</t>
+          <t>트빌리시 → 시그나기 왕복</t>
         </is>
       </c>
       <c r="C39" s="41" t="inlineStr">
         <is>
-          <t>A2 공항버스</t>
+          <t>마르슈르트카</t>
         </is>
       </c>
       <c r="D39" s="53" t="inlineStr">
         <is>
-          <t>시내</t>
+          <t>시외</t>
         </is>
       </c>
       <c r="E39" s="54" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F39" s="45" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="G39" s="48">
-        <f>ROUND(E39*환율!$B$7/1,0)</f>
+        <f>ROUND(E39*환율!$B$4/1,0)</f>
         <v/>
       </c>
       <c r="H39" s="55" t="inlineStr">
@@ -2559,176 +2559,44 @@
       </c>
       <c r="I39" s="43" t="inlineStr">
         <is>
-          <t>버스 4디르함 + 하필라트 카드 10디르함 · 칼리파 bin 자이드 St 승차 · 40~45분</t>
+          <t>삼고리 터미널 출발 · 편도 2~2.5시간 · 보드베는 요청하면 하차 · 돌아오는 막차 18~19시</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="38">
-      <c r="A40" s="45" t="inlineStr">
-        <is>
-          <t>9/28</t>
-        </is>
-      </c>
-      <c r="B40" s="41" t="inlineStr">
-        <is>
-          <t>예레반 → 가르니 왕복</t>
-        </is>
-      </c>
-      <c r="C40" s="41" t="inlineStr">
-        <is>
-          <t>266·284번 버스</t>
-        </is>
-      </c>
-      <c r="D40" s="53" t="inlineStr">
-        <is>
-          <t>시외</t>
-        </is>
-      </c>
-      <c r="E40" s="54" t="n">
-        <v>500</v>
-      </c>
-      <c r="F40" s="45" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="G40" s="48">
-        <f>ROUND(E40*환율!$B$5/1,0)</f>
-        <v/>
-      </c>
-      <c r="H40" s="55" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="I40" s="43" t="inlineStr">
-        <is>
-          <t>가이 정류장 출발 · 30분 간격 · 왕복 500드람</t>
-        </is>
-      </c>
+      <c r="A40" s="56" t="inlineStr">
+        <is>
+          <t>교통비 합계</t>
+        </is>
+      </c>
+      <c r="B40" s="57" t="n"/>
+      <c r="C40" s="57" t="n"/>
+      <c r="D40" s="57" t="n"/>
+      <c r="E40" s="57" t="n"/>
+      <c r="F40" s="57" t="n"/>
+      <c r="G40" s="58">
+        <f>SUM(G5:G39)</f>
+        <v/>
+      </c>
+      <c r="H40" s="57" t="n"/>
+      <c r="I40" s="57" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="38">
-      <c r="A41" s="45" t="inlineStr">
-        <is>
-          <t>9/24</t>
-        </is>
-      </c>
-      <c r="B41" s="41" t="inlineStr">
-        <is>
-          <t>스테판츠민다 → 주타 왕복</t>
-        </is>
-      </c>
-      <c r="C41" s="41" t="inlineStr">
-        <is>
-          <t>4WD 택시 (대기 포함)</t>
-        </is>
-      </c>
-      <c r="D41" s="53" t="inlineStr">
-        <is>
-          <t>시내</t>
-        </is>
-      </c>
-      <c r="E41" s="54" t="n">
-        <v>80</v>
-      </c>
-      <c r="F41" s="45" t="inlineStr">
-        <is>
-          <t>GEL</t>
-        </is>
-      </c>
-      <c r="G41" s="48">
-        <f>ROUND(E41*환율!$B$4/1,0)</f>
-        <v/>
-      </c>
-      <c r="H41" s="55" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="I41" s="43" t="inlineStr">
-        <is>
-          <t>대중교통 없음 · 25km 비포장 · 1인 단독이면 전액. 동행 구하면 40라리</t>
+      <c r="A41" s="37" t="inlineStr">
+        <is>
+          <t>택시 구간: 즈바리 · 주타 · 게하르트 · 노라방크 · 타테브 · 아부다비 10/4 시내 이동. 아테네(X95)·아부다비(A2) 새벽 공항행은 24시간 공항버스로 해결했습니다.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="38">
-      <c r="A42" s="45" t="inlineStr">
-        <is>
-          <t>9/25</t>
-        </is>
-      </c>
-      <c r="B42" s="41" t="inlineStr">
-        <is>
-          <t>트빌리시 → 시그나기 왕복</t>
-        </is>
-      </c>
-      <c r="C42" s="41" t="inlineStr">
-        <is>
-          <t>마르슈르트카</t>
-        </is>
-      </c>
-      <c r="D42" s="53" t="inlineStr">
-        <is>
-          <t>시외</t>
-        </is>
-      </c>
-      <c r="E42" s="54" t="n">
-        <v>25</v>
-      </c>
-      <c r="F42" s="45" t="inlineStr">
-        <is>
-          <t>GEL</t>
-        </is>
-      </c>
-      <c r="G42" s="48">
-        <f>ROUND(E42*환율!$B$4/1,0)</f>
-        <v/>
-      </c>
-      <c r="H42" s="55" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="I42" s="43" t="inlineStr">
-        <is>
-          <t>삼고리 터미널 출발 · 편도 2~2.5시간 · 보드베는 요청하면 하차 · 돌아오는 막차 18~19시</t>
+      <c r="A42" s="49" t="inlineStr">
+        <is>
+          <t>아부다비 10/4는 루브르(사디야트, 북쪽)와 모스크(알 마크타, 남쪽)가 정반대 방향이라 전 구간 택시로 잡았습니다. 루브르→모스크만 94번 버스로 바꾸면 75→2디르함이지만 60~75분이 걸립니다.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="38">
-      <c r="A43" s="56" t="inlineStr">
-        <is>
-          <t>교통비 합계</t>
-        </is>
-      </c>
-      <c r="B43" s="57" t="n"/>
-      <c r="C43" s="57" t="n"/>
-      <c r="D43" s="57" t="n"/>
-      <c r="E43" s="57" t="n"/>
-      <c r="F43" s="57" t="n"/>
-      <c r="G43" s="58">
-        <f>SUM(G5:G42)</f>
-        <v/>
-      </c>
-      <c r="H43" s="57" t="n"/>
-      <c r="I43" s="57" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="37" t="inlineStr">
-        <is>
-          <t>택시 구간: 즈바리 · 주타 · 게하르트 · 노라방크 · 타테브 · 아부다비 10/4 시내 이동. 아테네(X95)·아부다비(A2) 새벽 공항행은 24시간 공항버스로 해결했습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="49" t="inlineStr">
-        <is>
-          <t>아부다비 10/4는 루브르(사디야트, 북쪽)와 모스크(알 마크타, 남쪽)가 정반대 방향이라 전 구간 택시로 잡았습니다. 루브르→모스크만 94번 버스로 바꾸면 75→2디르함이지만 60~75분이 걸립니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="49" t="inlineStr">
+      <c r="A43" s="49" t="inlineStr">
         <is>
           <t>아부다비 10/4는 루브르(사디야트, 북쪽)와 모스크(알 마크타, 남쪽)가 정반대 방향이라 전 구간 택시로 잡았습니다. 루브르→모스크만 94번 버스로 바꾸면 75→2디르함이지만 60~75분이 걸립니다.</t>
         </is>
@@ -2747,7 +2615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="37" min="1" max="1"/>
@@ -3090,7 +2958,7 @@
     <row r="14" ht="15" customHeight="1" s="38">
       <c r="A14" s="45" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>9/30</t>
         </is>
       </c>
       <c r="B14" s="41" t="inlineStr">
@@ -3119,7 +2987,7 @@
     <row r="15" ht="15" customHeight="1" s="38">
       <c r="A15" s="45" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>9/30</t>
         </is>
       </c>
       <c r="B15" s="41" t="inlineStr">
@@ -3148,7 +3016,7 @@
     <row r="16" ht="15" customHeight="1" s="38">
       <c r="A16" s="45" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/1</t>
         </is>
       </c>
       <c r="B16" s="41" t="inlineStr">
@@ -3206,215 +3074,215 @@
     <row r="18" ht="15" customHeight="1" s="38">
       <c r="A18" s="45" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/3</t>
         </is>
       </c>
       <c r="B18" s="41" t="inlineStr">
         <is>
-          <t>노라방크</t>
+          <t>아크로폴리스</t>
         </is>
       </c>
       <c r="C18" s="54" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D18" s="45" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E18" s="48">
-        <f>ROUND(C18*환율!$B$5,0)</f>
+        <f>ROUND(C18*환율!$B$6,0)</f>
         <v/>
       </c>
       <c r="F18" s="47" t="inlineStr">
         <is>
-          <t>무료</t>
+          <t>hhticket.gr 공식 정가 30유로(연중 동일) · 타임드 엔트리 필수 · 60일 전 오픈, 성수기 5~7일 전 매진</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="38">
       <c r="A19" s="45" t="inlineStr">
         <is>
-          <t>10/1</t>
+          <t>10/3</t>
         </is>
       </c>
       <c r="B19" s="41" t="inlineStr">
         <is>
-          <t>윙스 오브 타테브 케이블카 왕복</t>
+          <t>고대 아고라 · 헤파이스토스 신전</t>
         </is>
       </c>
       <c r="C19" s="54" t="n">
-        <v>8000</v>
+        <v>12</v>
       </c>
       <c r="D19" s="45" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E19" s="48">
-        <f>ROUND(C19*환율!$B$5,0)</f>
+        <f>ROUND(C19*환율!$B$6,0)</f>
         <v/>
       </c>
       <c r="F19" s="47" t="inlineStr">
         <is>
-          <t>월요일 휴무</t>
+          <t>통합권 폐지로 별도 구매 필요 — 현장 확인</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="38">
       <c r="A20" s="45" t="inlineStr">
         <is>
-          <t>10/1</t>
+          <t>10/3</t>
         </is>
       </c>
       <c r="B20" s="41" t="inlineStr">
         <is>
-          <t>타테브 수도원</t>
+          <t>아크로폴리스 박물관</t>
         </is>
       </c>
       <c r="C20" s="54" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D20" s="45" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E20" s="48">
-        <f>ROUND(C20*환율!$B$5,0)</f>
+        <f>ROUND(C20*환율!$B$6,0)</f>
         <v/>
       </c>
       <c r="F20" s="47" t="inlineStr">
         <is>
-          <t>무료</t>
+          <t>실제 확인가 (별도 티켓)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="38">
       <c r="A21" s="45" t="inlineStr">
         <is>
-          <t>10/3</t>
+          <t>10/4</t>
         </is>
       </c>
       <c r="B21" s="41" t="inlineStr">
         <is>
-          <t>아크로폴리스</t>
+          <t>루브르 아부다비</t>
         </is>
       </c>
       <c r="C21" s="54" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="D21" s="45" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="E21" s="48">
-        <f>ROUND(C21*환율!$B$6,0)</f>
+        <f>ROUND(C21*환율!$B$7,0)</f>
         <v/>
       </c>
       <c r="F21" s="47" t="inlineStr">
         <is>
-          <t>hhticket.gr 공식 정가 30유로(연중 동일) · 타임드 엔트리 필수 · 60일 전 오픈, 성수기 5~7일 전 매진</t>
+          <t>10/4 일요일 10:00~20:30, 최종 입장 20:00 · 월요일 휴관 · 돔은 자정까지</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="38">
       <c r="A22" s="45" t="inlineStr">
         <is>
-          <t>10/3</t>
+          <t>10/4</t>
         </is>
       </c>
       <c r="B22" s="41" t="inlineStr">
         <is>
-          <t>고대 아고라 · 헤파이스토스 신전</t>
+          <t>셰이크 자이드 그랜드 모스크</t>
         </is>
       </c>
       <c r="C22" s="54" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D22" s="45" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="E22" s="48">
-        <f>ROUND(C22*환율!$B$6,0)</f>
+        <f>ROUND(C22*환율!$B$7,0)</f>
         <v/>
       </c>
       <c r="F22" s="47" t="inlineStr">
         <is>
-          <t>통합권 폐지로 별도 구매 필요 — 현장 확인</t>
+          <t>무료</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="38">
       <c r="A23" s="45" t="inlineStr">
         <is>
-          <t>10/3</t>
+          <t>9/27</t>
         </is>
       </c>
       <c r="B23" s="41" t="inlineStr">
         <is>
-          <t>아크로폴리스 박물관</t>
+          <t>지토그흐치안 도시생활박물관 (귬리)</t>
         </is>
       </c>
       <c r="C23" s="54" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="D23" s="45" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="E23" s="48">
-        <f>ROUND(C23*환율!$B$6,0)</f>
+        <f>ROUND(C23*환율!$B$5,0)</f>
         <v/>
       </c>
       <c r="F23" s="47" t="inlineStr">
         <is>
-          <t>실제 확인가 (별도 티켓)</t>
+          <t>화~금 10:00~17:00 · 일요일 개관 여부 현지 확인</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="38">
       <c r="A24" s="45" t="inlineStr">
         <is>
-          <t>10/4</t>
+          <t>9/29</t>
         </is>
       </c>
       <c r="B24" s="41" t="inlineStr">
         <is>
-          <t>루브르 아부다비</t>
+          <t>마테나다란 고문서관</t>
         </is>
       </c>
       <c r="C24" s="54" t="n">
-        <v>63</v>
+        <v>2000</v>
       </c>
       <c r="D24" s="45" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="E24" s="48">
-        <f>ROUND(C24*환율!$B$7,0)</f>
+        <f>ROUND(C24*환율!$B$5,0)</f>
         <v/>
       </c>
       <c r="F24" s="47" t="inlineStr">
         <is>
-          <t>10/4 일요일 10:00~20:30, 최종 입장 20:00 · 월요일 휴관 · 돔은 자정까지</t>
+          <t>화~토 10:00~17:50 · 일·월 휴관</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="38">
       <c r="A25" s="45" t="inlineStr">
         <is>
-          <t>10/4</t>
+          <t>9/29</t>
         </is>
       </c>
       <c r="B25" s="41" t="inlineStr">
         <is>
-          <t>셰이크 자이드 그랜드 모스크</t>
+          <t>카페시안 미술관</t>
         </is>
       </c>
       <c r="C25" s="54" t="n">
@@ -3422,37 +3290,124 @@
       </c>
       <c r="D25" s="45" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="E25" s="48">
-        <f>ROUND(C25*환율!$B$7,0)</f>
+        <f>ROUND(C25*환율!$B$5,0)</f>
         <v/>
       </c>
       <c r="F25" s="47" t="inlineStr">
         <is>
-          <t>무료</t>
+          <t>기부제 · 월요일 휴관</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="38">
-      <c r="A26" s="57" t="n"/>
-      <c r="B26" s="56" t="inlineStr">
+      <c r="A26" s="45" t="inlineStr">
+        <is>
+          <t>10/1</t>
+        </is>
+      </c>
+      <c r="B26" s="41" t="inlineStr">
+        <is>
+          <t>성 흐립시메 교회</t>
+        </is>
+      </c>
+      <c r="C26" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="45" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="E26" s="48">
+        <f>ROUND(C26*환율!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="F26" s="47" t="inlineStr">
+        <is>
+          <t>무료 · 유네스코</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="38">
+      <c r="A27" s="45" t="inlineStr">
+        <is>
+          <t>10/1</t>
+        </is>
+      </c>
+      <c r="B27" s="41" t="inlineStr">
+        <is>
+          <t>즈바르트노츠 유적</t>
+        </is>
+      </c>
+      <c r="C27" s="54" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D27" s="45" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="E27" s="48">
+        <f>ROUND(C27*환율!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="F27" s="47" t="inlineStr">
+        <is>
+          <t>7세기 원형 성당 터</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="38">
+      <c r="A28" s="45" t="inlineStr">
+        <is>
+          <t>10/1</t>
+        </is>
+      </c>
+      <c r="B28" s="41" t="inlineStr">
+        <is>
+          <t>대학살 추모관 박물관</t>
+        </is>
+      </c>
+      <c r="C28" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="45" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="E28" s="48">
+        <f>ROUND(C28*환율!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="F28" s="47" t="inlineStr">
+        <is>
+          <t>무료 · 17:00 마감 · 월요일 휴관</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="57" t="n"/>
+      <c r="B29" s="56" t="inlineStr">
         <is>
           <t>입장료 합계</t>
         </is>
       </c>
-      <c r="C26" s="57" t="n"/>
-      <c r="D26" s="57" t="n"/>
-      <c r="E26" s="58">
-        <f>SUM(E4:E25)</f>
-        <v/>
-      </c>
-      <c r="F26" s="57" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="38"/>
-    <row r="28" ht="15" customHeight="1" s="38">
-      <c r="A28" s="49" t="inlineStr">
+      <c r="C29" s="57" t="n"/>
+      <c r="D29" s="57" t="n"/>
+      <c r="E29" s="58">
+        <f>SUM(E4:E28)</f>
+        <v/>
+      </c>
+      <c r="F29" s="57" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="49" t="inlineStr">
         <is>
           <t>조지아·아르메니아 수도원은 대부분 무료입니다. 지출은 타테브 케이블카·아크로폴리스·루브르에 몰려 있습니다.</t>
         </is>
@@ -3572,7 +3527,7 @@
         </is>
       </c>
       <c r="D5" s="54">
-        <f>SUMIF(입장료!$A$4:$A$25,A5,입장료!$E$4:$E$25)</f>
+        <f>SUMIF(입장료!$A$4:$A$28,A5,입장료!$E$4:$E$28)</f>
         <v/>
       </c>
       <c r="E5" s="54" t="n">
@@ -3585,11 +3540,11 @@
         <v>6000</v>
       </c>
       <c r="H5" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A5,교통상세!$D$5:$D$42,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A5,교통상세!$D$5:$D$39,"시외")</f>
         <v/>
       </c>
       <c r="I5" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A5,교통상세!$D$5:$D$42,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A5,교통상세!$D$5:$D$39,"시내")</f>
         <v/>
       </c>
       <c r="J5" s="48">
@@ -3618,7 +3573,7 @@
         </is>
       </c>
       <c r="D6" s="54">
-        <f>SUMIF(입장료!$A$4:$A$25,A6,입장료!$E$4:$E$25)</f>
+        <f>SUMIF(입장료!$A$4:$A$28,A6,입장료!$E$4:$E$28)</f>
         <v/>
       </c>
       <c r="E6" s="54" t="n">
@@ -3631,11 +3586,11 @@
         <v>0</v>
       </c>
       <c r="H6" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A6,교통상세!$D$5:$D$42,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A6,교통상세!$D$5:$D$39,"시외")</f>
         <v/>
       </c>
       <c r="I6" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A6,교통상세!$D$5:$D$42,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A6,교통상세!$D$5:$D$39,"시내")</f>
         <v/>
       </c>
       <c r="J6" s="48">
@@ -3664,7 +3619,7 @@
         </is>
       </c>
       <c r="D7" s="54">
-        <f>SUMIF(입장료!$A$4:$A$25,A7,입장료!$E$4:$E$25)</f>
+        <f>SUMIF(입장료!$A$4:$A$28,A7,입장료!$E$4:$E$28)</f>
         <v/>
       </c>
       <c r="E7" s="54" t="n">
@@ -3677,11 +3632,11 @@
         <v>6000</v>
       </c>
       <c r="H7" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A7,교통상세!$D$5:$D$42,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A7,교통상세!$D$5:$D$39,"시외")</f>
         <v/>
       </c>
       <c r="I7" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A7,교통상세!$D$5:$D$42,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A7,교통상세!$D$5:$D$39,"시내")</f>
         <v/>
       </c>
       <c r="J7" s="48">
@@ -3710,7 +3665,7 @@
         </is>
       </c>
       <c r="D8" s="54">
-        <f>SUMIF(입장료!$A$4:$A$25,A8,입장료!$E$4:$E$25)</f>
+        <f>SUMIF(입장료!$A$4:$A$28,A8,입장료!$E$4:$E$28)</f>
         <v/>
       </c>
       <c r="E8" s="54" t="n">
@@ -3723,11 +3678,11 @@
         <v>6000</v>
       </c>
       <c r="H8" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A8,교통상세!$D$5:$D$42,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A8,교통상세!$D$5:$D$39,"시외")</f>
         <v/>
       </c>
       <c r="I8" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A8,교통상세!$D$5:$D$42,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A8,교통상세!$D$5:$D$39,"시내")</f>
         <v/>
       </c>
       <c r="J8" s="48">
@@ -3756,7 +3711,7 @@
         </is>
       </c>
       <c r="D9" s="54">
-        <f>SUMIF(입장료!$A$4:$A$25,A9,입장료!$E$4:$E$25)</f>
+        <f>SUMIF(입장료!$A$4:$A$28,A9,입장료!$E$4:$E$28)</f>
         <v/>
       </c>
       <c r="E9" s="54" t="n">
@@ -3769,11 +3724,11 @@
         <v>5000</v>
       </c>
       <c r="H9" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A9,교통상세!$D$5:$D$42,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A9,교통상세!$D$5:$D$39,"시외")</f>
         <v/>
       </c>
       <c r="I9" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A9,교통상세!$D$5:$D$42,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A9,교통상세!$D$5:$D$39,"시내")</f>
         <v/>
       </c>
       <c r="J9" s="48">
@@ -3802,7 +3757,7 @@
         </is>
       </c>
       <c r="D10" s="54">
-        <f>SUMIF(입장료!$A$4:$A$25,A10,입장료!$E$4:$E$25)</f>
+        <f>SUMIF(입장료!$A$4:$A$28,A10,입장료!$E$4:$E$28)</f>
         <v/>
       </c>
       <c r="E10" s="54" t="n">
@@ -3815,11 +3770,11 @@
         <v>5000</v>
       </c>
       <c r="H10" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A10,교통상세!$D$5:$D$42,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A10,교통상세!$D$5:$D$39,"시외")</f>
         <v/>
       </c>
       <c r="I10" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A10,교통상세!$D$5:$D$42,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A10,교통상세!$D$5:$D$39,"시내")</f>
         <v/>
       </c>
       <c r="J10" s="48">
@@ -3848,7 +3803,7 @@
         </is>
       </c>
       <c r="D11" s="54">
-        <f>SUMIF(입장료!$A$4:$A$25,A11,입장료!$E$4:$E$25)</f>
+        <f>SUMIF(입장료!$A$4:$A$28,A11,입장료!$E$4:$E$28)</f>
         <v/>
       </c>
       <c r="E11" s="54" t="n">
@@ -3861,11 +3816,11 @@
         <v>5000</v>
       </c>
       <c r="H11" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A11,교통상세!$D$5:$D$42,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A11,교통상세!$D$5:$D$39,"시외")</f>
         <v/>
       </c>
       <c r="I11" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A11,교통상세!$D$5:$D$42,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A11,교통상세!$D$5:$D$39,"시내")</f>
         <v/>
       </c>
       <c r="J11" s="48">
@@ -3894,7 +3849,7 @@
         </is>
       </c>
       <c r="D12" s="54">
-        <f>SUMIF(입장료!$A$4:$A$25,A12,입장료!$E$4:$E$25)</f>
+        <f>SUMIF(입장료!$A$4:$A$28,A12,입장료!$E$4:$E$28)</f>
         <v/>
       </c>
       <c r="E12" s="54" t="n">
@@ -3907,11 +3862,11 @@
         <v>5000</v>
       </c>
       <c r="H12" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A12,교통상세!$D$5:$D$42,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A12,교통상세!$D$5:$D$39,"시외")</f>
         <v/>
       </c>
       <c r="I12" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A12,교통상세!$D$5:$D$42,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A12,교통상세!$D$5:$D$39,"시내")</f>
         <v/>
       </c>
       <c r="J12" s="48">
@@ -3936,11 +3891,11 @@
       </c>
       <c r="C13" s="66" t="inlineStr">
         <is>
-          <t>예레반 — 베르니사쥬·캐스케이드</t>
+          <t>귬리 — 쿠마이리 구시가</t>
         </is>
       </c>
       <c r="D13" s="54">
-        <f>SUMIF(입장료!$A$4:$A$25,A13,입장료!$E$4:$E$25)</f>
+        <f>SUMIF(입장료!$A$4:$A$28,A13,입장료!$E$4:$E$28)</f>
         <v/>
       </c>
       <c r="E13" s="54" t="n">
@@ -3953,11 +3908,11 @@
         <v>5000</v>
       </c>
       <c r="H13" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A13,교통상세!$D$5:$D$42,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A13,교통상세!$D$5:$D$39,"시외")</f>
         <v/>
       </c>
       <c r="I13" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A13,교통상세!$D$5:$D$42,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A13,교통상세!$D$5:$D$39,"시내")</f>
         <v/>
       </c>
       <c r="J13" s="48">
@@ -3982,11 +3937,11 @@
       </c>
       <c r="C14" s="66" t="inlineStr">
         <is>
-          <t>예레반 — 가르니·게하르트</t>
+          <t>예레반 — 귬리에서 이동 · 시내</t>
         </is>
       </c>
       <c r="D14" s="54">
-        <f>SUMIF(입장료!$A$4:$A$25,A14,입장료!$E$4:$E$25)</f>
+        <f>SUMIF(입장료!$A$4:$A$28,A14,입장료!$E$4:$E$28)</f>
         <v/>
       </c>
       <c r="E14" s="54" t="n">
@@ -3999,11 +3954,11 @@
         <v>6000</v>
       </c>
       <c r="H14" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A14,교통상세!$D$5:$D$42,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A14,교통상세!$D$5:$D$39,"시외")</f>
         <v/>
       </c>
       <c r="I14" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A14,교통상세!$D$5:$D$42,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A14,교통상세!$D$5:$D$39,"시내")</f>
         <v/>
       </c>
       <c r="J14" s="48">
@@ -4028,11 +3983,11 @@
       </c>
       <c r="C15" s="66" t="inlineStr">
         <is>
-          <t>예레반 — 에치미아진·코르 비랍</t>
+          <t>예레반 — 코르 비랍·마테나다란</t>
         </is>
       </c>
       <c r="D15" s="54">
-        <f>SUMIF(입장료!$A$4:$A$25,A15,입장료!$E$4:$E$25)</f>
+        <f>SUMIF(입장료!$A$4:$A$28,A15,입장료!$E$4:$E$28)</f>
         <v/>
       </c>
       <c r="E15" s="54" t="n">
@@ -4045,11 +4000,11 @@
         <v>6000</v>
       </c>
       <c r="H15" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A15,교통상세!$D$5:$D$42,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A15,교통상세!$D$5:$D$39,"시외")</f>
         <v/>
       </c>
       <c r="I15" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A15,교통상세!$D$5:$D$42,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A15,교통상세!$D$5:$D$39,"시내")</f>
         <v/>
       </c>
       <c r="J15" s="48">
@@ -4074,28 +4029,28 @@
       </c>
       <c r="C16" s="66" t="inlineStr">
         <is>
-          <t>고리스 — 노라방크</t>
+          <t>예레반 — 가르니·게하르트</t>
         </is>
       </c>
       <c r="D16" s="54">
-        <f>SUMIF(입장료!$A$4:$A$25,A16,입장료!$E$4:$E$25)</f>
+        <f>SUMIF(입장료!$A$4:$A$28,A16,입장료!$E$4:$E$28)</f>
         <v/>
       </c>
       <c r="E16" s="54" t="n">
         <v>30000</v>
       </c>
       <c r="F16" s="54" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="G16" s="54" t="n">
         <v>5000</v>
       </c>
       <c r="H16" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A16,교통상세!$D$5:$D$42,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A16,교통상세!$D$5:$D$39,"시외")</f>
         <v/>
       </c>
       <c r="I16" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A16,교통상세!$D$5:$D$42,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A16,교통상세!$D$5:$D$39,"시내")</f>
         <v/>
       </c>
       <c r="J16" s="48">
@@ -4120,11 +4075,11 @@
       </c>
       <c r="C17" s="66" t="inlineStr">
         <is>
-          <t>예레반 복귀 — 타테브</t>
+          <t>예레반 — 에치미아진·즈바르트노츠</t>
         </is>
       </c>
       <c r="D17" s="54">
-        <f>SUMIF(입장료!$A$4:$A$25,A17,입장료!$E$4:$E$25)</f>
+        <f>SUMIF(입장료!$A$4:$A$28,A17,입장료!$E$4:$E$28)</f>
         <v/>
       </c>
       <c r="E17" s="54" t="n">
@@ -4137,11 +4092,11 @@
         <v>5000</v>
       </c>
       <c r="H17" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A17,교통상세!$D$5:$D$42,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A17,교통상세!$D$5:$D$39,"시외")</f>
         <v/>
       </c>
       <c r="I17" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A17,교통상세!$D$5:$D$42,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A17,교통상세!$D$5:$D$39,"시내")</f>
         <v/>
       </c>
       <c r="J17" s="48">
@@ -4170,7 +4125,7 @@
         </is>
       </c>
       <c r="D18" s="54">
-        <f>SUMIF(입장료!$A$4:$A$25,A18,입장료!$E$4:$E$25)</f>
+        <f>SUMIF(입장료!$A$4:$A$28,A18,입장료!$E$4:$E$28)</f>
         <v/>
       </c>
       <c r="E18" s="54" t="n">
@@ -4183,11 +4138,11 @@
         <v>6000</v>
       </c>
       <c r="H18" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A18,교통상세!$D$5:$D$42,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A18,교통상세!$D$5:$D$39,"시외")</f>
         <v/>
       </c>
       <c r="I18" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A18,교통상세!$D$5:$D$42,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A18,교통상세!$D$5:$D$39,"시내")</f>
         <v/>
       </c>
       <c r="J18" s="48">
@@ -4216,7 +4171,7 @@
         </is>
       </c>
       <c r="D19" s="54">
-        <f>SUMIF(입장료!$A$4:$A$25,A19,입장료!$E$4:$E$25)</f>
+        <f>SUMIF(입장료!$A$4:$A$28,A19,입장료!$E$4:$E$28)</f>
         <v/>
       </c>
       <c r="E19" s="54" t="n">
@@ -4229,11 +4184,11 @@
         <v>8000</v>
       </c>
       <c r="H19" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A19,교통상세!$D$5:$D$42,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A19,교통상세!$D$5:$D$39,"시외")</f>
         <v/>
       </c>
       <c r="I19" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A19,교통상세!$D$5:$D$42,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A19,교통상세!$D$5:$D$39,"시내")</f>
         <v/>
       </c>
       <c r="J19" s="48">
@@ -4262,7 +4217,7 @@
         </is>
       </c>
       <c r="D20" s="54">
-        <f>SUMIF(입장료!$A$4:$A$25,A20,입장료!$E$4:$E$25)</f>
+        <f>SUMIF(입장료!$A$4:$A$28,A20,입장료!$E$4:$E$28)</f>
         <v/>
       </c>
       <c r="E20" s="54" t="n">
@@ -4275,11 +4230,11 @@
         <v>8000</v>
       </c>
       <c r="H20" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A20,교통상세!$D$5:$D$42,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A20,교통상세!$D$5:$D$39,"시외")</f>
         <v/>
       </c>
       <c r="I20" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A20,교통상세!$D$5:$D$42,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A20,교통상세!$D$5:$D$39,"시내")</f>
         <v/>
       </c>
       <c r="J20" s="48">
@@ -4308,7 +4263,7 @@
         </is>
       </c>
       <c r="D21" s="54">
-        <f>SUMIF(입장료!$A$4:$A$25,A21,입장료!$E$4:$E$25)</f>
+        <f>SUMIF(입장료!$A$4:$A$28,A21,입장료!$E$4:$E$28)</f>
         <v/>
       </c>
       <c r="E21" s="54" t="n">
@@ -4321,11 +4276,11 @@
         <v>0</v>
       </c>
       <c r="H21" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A21,교통상세!$D$5:$D$42,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A21,교통상세!$D$5:$D$39,"시외")</f>
         <v/>
       </c>
       <c r="I21" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$42,교통상세!$A$5:$A$42,A21,교통상세!$D$5:$D$42,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A21,교통상세!$D$5:$D$39,"시내")</f>
         <v/>
       </c>
       <c r="J21" s="48">

--- a/여행예산_상하이반영.xlsx
+++ b/여행예산_상하이반영.xlsx
@@ -846,11 +846,7 @@
       <c r="B10" s="42" t="n">
         <v>446000</v>
       </c>
-      <c r="C10" s="47" t="inlineStr">
-        <is>
-          <t>결제 완료 — 원화 확정. 김포→상하이 + 푸동→트빌리시 2편 합산</t>
-        </is>
-      </c>
+      <c r="C10" s="47" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="38">
       <c r="A11" s="41" t="inlineStr">
@@ -861,11 +857,7 @@
       <c r="B11" s="42" t="n">
         <v>303900</v>
       </c>
-      <c r="C11" s="47" t="inlineStr">
-        <is>
-          <t>결제 완료 — 원화 확정</t>
-        </is>
-      </c>
+      <c r="C11" s="47" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="38">
       <c r="A12" s="41" t="inlineStr">
@@ -876,27 +868,12 @@
       <c r="B12" s="42" t="n">
         <v>656700</v>
       </c>
-      <c r="C12" s="47" t="inlineStr">
-        <is>
-          <t>결제 완료 — 원화 확정. 환율이 바뀌어도 이 금액은 그대로</t>
-        </is>
-      </c>
+      <c r="C12" s="47" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="38">
-      <c r="A13" s="41" t="inlineStr">
-        <is>
-          <t>항공권 합계</t>
-        </is>
-      </c>
-      <c r="B13" s="48">
-        <f>SUM(B10:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="43" t="inlineStr">
-        <is>
-          <t>3편 모두 결제 완료. 이후 환율 변동은 현지 지출에만 영향</t>
-        </is>
-      </c>
+      <c r="A13" s="41" t="n"/>
+      <c r="B13" s="48" t="n"/>
+      <c r="C13" s="43" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="38">
       <c r="A14" s="41" t="inlineStr">
@@ -948,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="37" min="1" max="1"/>
@@ -1774,17 +1751,17 @@
     <row r="22" ht="15" customHeight="1" s="38">
       <c r="A22" s="45" t="inlineStr">
         <is>
-          <t>10/2</t>
+          <t>9/29</t>
         </is>
       </c>
       <c r="B22" s="41" t="inlineStr">
         <is>
-          <t>예레반 → 세반 왕복</t>
+          <t>예레반 → 코르 비랍 · 노라방크 · 타테브 (왕복)</t>
         </is>
       </c>
       <c r="C22" s="41" t="inlineStr">
         <is>
-          <t>마르슈르트카</t>
+          <t>1일 그룹투어 (미니버스)</t>
         </is>
       </c>
       <c r="D22" s="53" t="inlineStr">
@@ -1793,7 +1770,7 @@
         </is>
       </c>
       <c r="E22" s="54" t="n">
-        <v>2500</v>
+        <v>25000</v>
       </c>
       <c r="F22" s="45" t="inlineStr">
         <is>
@@ -1806,29 +1783,29 @@
       </c>
       <c r="H22" s="55" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="I22" s="47" t="inlineStr">
         <is>
-          <t>편도 1,000~1,500드람 · 편도 1~1.5시간</t>
+          <t>Hyur Service 63.72달러 · 입장료·케이블카 포함, 점심 별도 · 08:30~22:30</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="38">
       <c r="A23" s="45" t="inlineStr">
         <is>
-          <t>10/2</t>
+          <t>9/27</t>
         </is>
       </c>
       <c r="B23" s="41" t="inlineStr">
         <is>
-          <t>세반 → 세바나방크 반도</t>
+          <t>킬리키아 터미널 → 시내</t>
         </is>
       </c>
       <c r="C23" s="41" t="inlineStr">
         <is>
-          <t>도보 또는 택시</t>
+          <t>버스</t>
         </is>
       </c>
       <c r="D23" s="53" t="inlineStr">
@@ -1837,7 +1814,7 @@
         </is>
       </c>
       <c r="E23" s="54" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F23" s="45" t="inlineStr">
         <is>
@@ -1850,29 +1827,29 @@
       </c>
       <c r="H23" s="55" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>○</t>
         </is>
       </c>
       <c r="I23" s="43" t="inlineStr">
         <is>
-          <t>도보 30분 · 1인 단독이라 전액 부담</t>
+          <t>또는 얀덱스 택시</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="38">
       <c r="A24" s="45" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>9/30</t>
         </is>
       </c>
       <c r="B24" s="41" t="inlineStr">
         <is>
-          <t>킬리키아 터미널 → 시내</t>
+          <t>가르니 → 게하르트 왕복</t>
         </is>
       </c>
       <c r="C24" s="41" t="inlineStr">
         <is>
-          <t>버스</t>
+          <t>택시</t>
         </is>
       </c>
       <c r="D24" s="53" t="inlineStr">
@@ -1881,7 +1858,7 @@
         </is>
       </c>
       <c r="E24" s="54" t="n">
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="F24" s="45" t="inlineStr">
         <is>
@@ -1894,29 +1871,29 @@
       </c>
       <c r="H24" s="55" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="I24" s="47" t="inlineStr">
         <is>
-          <t>또는 얀덱스 택시</t>
+          <t>9km, 대중교통 없음 · 1인 단독이라 전액 부담</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="38">
       <c r="A25" s="45" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/1</t>
         </is>
       </c>
       <c r="B25" s="41" t="inlineStr">
         <is>
-          <t>가르니 → 게하르트 왕복</t>
+          <t>예레반 → 에치미아진 왕복</t>
         </is>
       </c>
       <c r="C25" s="41" t="inlineStr">
         <is>
-          <t>택시</t>
+          <t>마르슈르트카</t>
         </is>
       </c>
       <c r="D25" s="53" t="inlineStr">
@@ -1925,7 +1902,7 @@
         </is>
       </c>
       <c r="E25" s="54" t="n">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="F25" s="45" t="inlineStr">
         <is>
@@ -1938,29 +1915,29 @@
       </c>
       <c r="H25" s="55" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>○</t>
         </is>
       </c>
       <c r="I25" s="47" t="inlineStr">
         <is>
-          <t>9km, 대중교통 없음 · 1인 단독이라 전액 부담</t>
+          <t>킬리키아 터미널</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="38">
       <c r="A26" s="45" t="inlineStr">
         <is>
-          <t>10/1</t>
+          <t>10/3</t>
         </is>
       </c>
       <c r="B26" s="41" t="inlineStr">
         <is>
-          <t>예레반 → 에치미아진 왕복</t>
+          <t>예레반 → 즈바르트노츠 공항</t>
         </is>
       </c>
       <c r="C26" s="41" t="inlineStr">
         <is>
-          <t>마르슈르트카</t>
+          <t>택시</t>
         </is>
       </c>
       <c r="D26" s="53" t="inlineStr">
@@ -1969,7 +1946,7 @@
         </is>
       </c>
       <c r="E26" s="54" t="n">
-        <v>600</v>
+        <v>4000</v>
       </c>
       <c r="F26" s="45" t="inlineStr">
         <is>
@@ -1982,29 +1959,29 @@
       </c>
       <c r="H26" s="55" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>△</t>
         </is>
       </c>
       <c r="I26" s="47" t="inlineStr">
         <is>
-          <t>킬리키아 터미널</t>
+          <t>01:30경 출발, 심야 할증 감안</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="38">
       <c r="A27" s="45" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/3</t>
         </is>
       </c>
       <c r="B27" s="41" t="inlineStr">
         <is>
-          <t>예레반 → 코르 비랍 왕복</t>
+          <t>아테네 공항 → 신타그마역</t>
         </is>
       </c>
       <c r="C27" s="41" t="inlineStr">
         <is>
-          <t>마르슈르트카</t>
+          <t>메트로 3호선</t>
         </is>
       </c>
       <c r="D27" s="53" t="inlineStr">
@@ -2013,25 +1990,25 @@
         </is>
       </c>
       <c r="E27" s="54" t="n">
-        <v>1200</v>
+        <v>10</v>
       </c>
       <c r="F27" s="45" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G27" s="48">
-        <f>ROUND(E27*환율!$B$5/1,0)</f>
+        <f>ROUND(E27*환율!$B$6/1,0)</f>
         <v/>
       </c>
       <c r="H27" s="55" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>○</t>
         </is>
       </c>
       <c r="I27" s="43" t="inlineStr">
         <is>
-          <t>하루 몇 편뿐</t>
+          <t>공항선 정액 10유로, 40분</t>
         </is>
       </c>
     </row>
@@ -2043,12 +2020,12 @@
       </c>
       <c r="B28" s="41" t="inlineStr">
         <is>
-          <t>예레반 → 즈바르트노츠 공항</t>
+          <t>아테네 시내 이동</t>
         </is>
       </c>
       <c r="C28" s="41" t="inlineStr">
         <is>
-          <t>택시</t>
+          <t>메트로·트램 4~5회</t>
         </is>
       </c>
       <c r="D28" s="53" t="inlineStr">
@@ -2057,42 +2034,42 @@
         </is>
       </c>
       <c r="E28" s="54" t="n">
-        <v>4000</v>
+        <v>6</v>
       </c>
       <c r="F28" s="45" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G28" s="48">
-        <f>ROUND(E28*환율!$B$5/1,0)</f>
+        <f>ROUND(E28*환율!$B$6/1,0)</f>
         <v/>
       </c>
       <c r="H28" s="55" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>○</t>
         </is>
       </c>
       <c r="I28" s="47" t="inlineStr">
         <is>
-          <t>01:30경 출발, 심야 할증 감안</t>
+          <t>1회 1.20유로. 대부분 도보권이라 보조 수단</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="38">
       <c r="A29" s="45" t="inlineStr">
         <is>
-          <t>10/3</t>
+          <t>10/4</t>
         </is>
       </c>
       <c r="B29" s="41" t="inlineStr">
         <is>
-          <t>아테네 공항 → 신타그마역</t>
+          <t>아테네 → 공항 (04:10 출발)</t>
         </is>
       </c>
       <c r="C29" s="41" t="inlineStr">
         <is>
-          <t>메트로 3호선</t>
+          <t>X95 공항버스</t>
         </is>
       </c>
       <c r="D29" s="53" t="inlineStr">
@@ -2101,7 +2078,7 @@
         </is>
       </c>
       <c r="E29" s="54" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="F29" s="45" t="inlineStr">
         <is>
@@ -2119,24 +2096,24 @@
       </c>
       <c r="I29" s="43" t="inlineStr">
         <is>
-          <t>공항선 정액 10유로, 40분</t>
+          <t>신타그마 발 24시간 운행 · 야간 60분 간격이라 03:55까지 정류장 도착 · 승차권은 전날 지하철역에서 미리 구입 · 택시는 심야 정액 55유로</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="38">
       <c r="A30" s="45" t="inlineStr">
         <is>
-          <t>10/3</t>
+          <t>10/4</t>
         </is>
       </c>
       <c r="B30" s="41" t="inlineStr">
         <is>
-          <t>아테네 시내 이동</t>
+          <t>자이드 국제공항 → TRYP 호텔</t>
         </is>
       </c>
       <c r="C30" s="41" t="inlineStr">
         <is>
-          <t>메트로·트램 4~5회</t>
+          <t>택시</t>
         </is>
       </c>
       <c r="D30" s="53" t="inlineStr">
@@ -2145,25 +2122,25 @@
         </is>
       </c>
       <c r="E30" s="54" t="n">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="F30" s="45" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="G30" s="48">
-        <f>ROUND(E30*환율!$B$6/1,0)</f>
+        <f>ROUND(E30*환율!$B$7/1,0)</f>
         <v/>
       </c>
       <c r="H30" s="55" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="I30" s="47" t="inlineStr">
         <is>
-          <t>1회 1.20유로. 대부분 도보권이라 보조 수단</t>
+          <t>칼리파 bin 자이드 St · 30~40분 · 미터 약 85~100디르함</t>
         </is>
       </c>
     </row>
@@ -2175,12 +2152,12 @@
       </c>
       <c r="B31" s="41" t="inlineStr">
         <is>
-          <t>아테네 → 공항 (04:10 출발)</t>
+          <t>TRYP 호텔 → 루브르 아부다비</t>
         </is>
       </c>
       <c r="C31" s="41" t="inlineStr">
         <is>
-          <t>X95 공항버스</t>
+          <t>택시</t>
         </is>
       </c>
       <c r="D31" s="53" t="inlineStr">
@@ -2189,25 +2166,25 @@
         </is>
       </c>
       <c r="E31" s="54" t="n">
-        <v>6.2</v>
+        <v>45</v>
       </c>
       <c r="F31" s="45" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="G31" s="48">
-        <f>ROUND(E31*환율!$B$6/1,0)</f>
+        <f>ROUND(E31*환율!$B$7/1,0)</f>
         <v/>
       </c>
       <c r="H31" s="55" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="I31" s="43" t="inlineStr">
         <is>
-          <t>신타그마 발 24시간 운행 · 야간 60분 간격이라 03:55까지 정류장 도착 · 승차권은 전날 지하철역에서 미리 구입 · 택시는 심야 정액 55유로</t>
+          <t>사디야트 섬 · 약 14km, 20~25분</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2196,7 @@
       </c>
       <c r="B32" s="41" t="inlineStr">
         <is>
-          <t>자이드 국제공항 → TRYP 호텔</t>
+          <t>루브르 → 셰이크 자이드 모스크</t>
         </is>
       </c>
       <c r="C32" s="41" t="inlineStr">
@@ -2233,7 +2210,7 @@
         </is>
       </c>
       <c r="E32" s="54" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="F32" s="45" t="inlineStr">
         <is>
@@ -2251,7 +2228,7 @@
       </c>
       <c r="I32" s="47" t="inlineStr">
         <is>
-          <t>칼리파 bin 자이드 St · 30~40분 · 미터 약 85~100디르함</t>
+          <t>섬 반대편 횡단 약 28km, 30~35분 · 94번 버스면 2디르함이나 60~75분</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2240,7 @@
       </c>
       <c r="B33" s="41" t="inlineStr">
         <is>
-          <t>TRYP 호텔 → 루브르 아부다비</t>
+          <t>모스크 → TRYP 호텔</t>
         </is>
       </c>
       <c r="C33" s="41" t="inlineStr">
@@ -2295,24 +2272,24 @@
       </c>
       <c r="I33" s="43" t="inlineStr">
         <is>
-          <t>사디야트 섬 · 약 14km, 20~25분</t>
+          <t>약 14km, 18~20분</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="38">
       <c r="A34" s="45" t="inlineStr">
         <is>
-          <t>10/4</t>
+          <t>10/5</t>
         </is>
       </c>
       <c r="B34" s="41" t="inlineStr">
         <is>
-          <t>루브르 → 셰이크 자이드 모스크</t>
+          <t>TRYP 호텔 → 공항 (05:30)</t>
         </is>
       </c>
       <c r="C34" s="41" t="inlineStr">
         <is>
-          <t>택시</t>
+          <t>A2 공항버스</t>
         </is>
       </c>
       <c r="D34" s="53" t="inlineStr">
@@ -2321,7 +2298,7 @@
         </is>
       </c>
       <c r="E34" s="54" t="n">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="F34" s="45" t="inlineStr">
         <is>
@@ -2334,73 +2311,73 @@
       </c>
       <c r="H34" s="55" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>○</t>
         </is>
       </c>
       <c r="I34" s="47" t="inlineStr">
         <is>
-          <t>섬 반대편 횡단 약 28km, 30~35분 · 94번 버스면 2디르함이나 60~75분</t>
+          <t>버스 4디르함 + 하필라트 카드 10디르함 · 칼리파 bin 자이드 St 승차 · 40~45분</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="38">
       <c r="A35" s="45" t="inlineStr">
         <is>
-          <t>10/4</t>
+          <t>9/30</t>
         </is>
       </c>
       <c r="B35" s="41" t="inlineStr">
         <is>
-          <t>모스크 → TRYP 호텔</t>
+          <t>예레반 → 가르니 왕복</t>
         </is>
       </c>
       <c r="C35" s="41" t="inlineStr">
         <is>
-          <t>택시</t>
+          <t>266·284번 버스</t>
         </is>
       </c>
       <c r="D35" s="53" t="inlineStr">
         <is>
-          <t>시내</t>
+          <t>시외</t>
         </is>
       </c>
       <c r="E35" s="54" t="n">
-        <v>45</v>
+        <v>500</v>
       </c>
       <c r="F35" s="45" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="G35" s="48">
-        <f>ROUND(E35*환율!$B$7/1,0)</f>
+        <f>ROUND(E35*환율!$B$5/1,0)</f>
         <v/>
       </c>
       <c r="H35" s="55" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>○</t>
         </is>
       </c>
       <c r="I35" s="43" t="inlineStr">
         <is>
-          <t>약 14km, 18~20분</t>
+          <t>가이 정류장 출발 · 30분 간격 · 왕복 500드람</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="38">
       <c r="A36" s="45" t="inlineStr">
         <is>
-          <t>10/5</t>
+          <t>9/24</t>
         </is>
       </c>
       <c r="B36" s="41" t="inlineStr">
         <is>
-          <t>TRYP 호텔 → 공항 (05:30)</t>
+          <t>스테판츠민다 → 주타 왕복</t>
         </is>
       </c>
       <c r="C36" s="41" t="inlineStr">
         <is>
-          <t>A2 공항버스</t>
+          <t>4WD 택시 (대기 포함)</t>
         </is>
       </c>
       <c r="D36" s="53" t="inlineStr">
@@ -2409,42 +2386,42 @@
         </is>
       </c>
       <c r="E36" s="54" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="F36" s="45" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="G36" s="48">
-        <f>ROUND(E36*환율!$B$7/1,0)</f>
+        <f>ROUND(E36*환율!$B$4/1,0)</f>
         <v/>
       </c>
       <c r="H36" s="55" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="I36" s="47" t="inlineStr">
         <is>
-          <t>버스 4디르함 + 하필라트 카드 10디르함 · 칼리파 bin 자이드 St 승차 · 40~45분</t>
+          <t>대중교통 없음 · 25km 비포장 · 1인 단독이면 전액. 동행 구하면 40라리</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="38">
       <c r="A37" s="45" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>9/25</t>
         </is>
       </c>
       <c r="B37" s="41" t="inlineStr">
         <is>
-          <t>예레반 → 가르니 왕복</t>
+          <t>트빌리시 → 시그나기 왕복</t>
         </is>
       </c>
       <c r="C37" s="41" t="inlineStr">
         <is>
-          <t>266·284번 버스</t>
+          <t>마르슈르트카</t>
         </is>
       </c>
       <c r="D37" s="53" t="inlineStr">
@@ -2453,15 +2430,15 @@
         </is>
       </c>
       <c r="E37" s="54" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="F37" s="45" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="G37" s="48">
-        <f>ROUND(E37*환율!$B$5/1,0)</f>
+        <f>ROUND(E37*환율!$B$4/1,0)</f>
         <v/>
       </c>
       <c r="H37" s="55" t="inlineStr">
@@ -2471,24 +2448,24 @@
       </c>
       <c r="I37" s="47" t="inlineStr">
         <is>
-          <t>가이 정류장 출발 · 30분 간격 · 왕복 500드람</t>
+          <t>삼고리 터미널 출발 · 편도 2~2.5시간 · 보드베는 요청하면 하차 · 돌아오는 막차 18~19시</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="38">
       <c r="A38" s="45" t="inlineStr">
         <is>
-          <t>9/24</t>
+          <t>9/29</t>
         </is>
       </c>
       <c r="B38" s="41" t="inlineStr">
         <is>
-          <t>스테판츠민다 → 주타 왕복</t>
+          <t>투어 사무실 → 숙소 (심야)</t>
         </is>
       </c>
       <c r="C38" s="41" t="inlineStr">
         <is>
-          <t>4WD 택시 (대기 포함)</t>
+          <t>택시 또는 도보</t>
         </is>
       </c>
       <c r="D38" s="53" t="inlineStr">
@@ -2497,111 +2474,69 @@
         </is>
       </c>
       <c r="E38" s="54" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="F38" s="45" t="inlineStr">
         <is>
-          <t>GEL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="G38" s="48">
-        <f>ROUND(E38*환율!$B$4/1,0)</f>
+        <f>ROUND(E38*환율!$B$5/1,0)</f>
         <v/>
       </c>
       <c r="H38" s="55" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>△</t>
         </is>
       </c>
       <c r="I38" s="47" t="inlineStr">
         <is>
-          <t>대중교통 없음 · 25km 비포장 · 1인 단독이면 전액. 동행 구하면 40라리</t>
+          <t>22:30 이후 날반댠 96번지 하차 · 도보 10분이면 0원</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="38">
-      <c r="A39" s="45" t="inlineStr">
-        <is>
-          <t>9/25</t>
-        </is>
-      </c>
-      <c r="B39" s="41" t="inlineStr">
-        <is>
-          <t>트빌리시 → 시그나기 왕복</t>
-        </is>
-      </c>
-      <c r="C39" s="41" t="inlineStr">
-        <is>
-          <t>마르슈르트카</t>
-        </is>
-      </c>
-      <c r="D39" s="53" t="inlineStr">
-        <is>
-          <t>시외</t>
-        </is>
-      </c>
-      <c r="E39" s="54" t="n">
-        <v>25</v>
-      </c>
-      <c r="F39" s="45" t="inlineStr">
-        <is>
-          <t>GEL</t>
-        </is>
-      </c>
-      <c r="G39" s="48">
-        <f>ROUND(E39*환율!$B$4/1,0)</f>
-        <v/>
-      </c>
-      <c r="H39" s="55" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="I39" s="43" t="inlineStr">
-        <is>
-          <t>삼고리 터미널 출발 · 편도 2~2.5시간 · 보드베는 요청하면 하차 · 돌아오는 막차 18~19시</t>
-        </is>
-      </c>
+      <c r="A39" s="56" t="inlineStr">
+        <is>
+          <t>교통비 합계</t>
+        </is>
+      </c>
+      <c r="B39" s="57" t="n"/>
+      <c r="C39" s="57" t="n"/>
+      <c r="D39" s="57" t="n"/>
+      <c r="E39" s="57" t="n"/>
+      <c r="F39" s="57" t="n"/>
+      <c r="G39" s="58">
+        <f>SUM(G5:G38)</f>
+        <v/>
+      </c>
+      <c r="H39" s="57" t="n"/>
+      <c r="I39" s="57" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="38">
-      <c r="A40" s="56" t="inlineStr">
-        <is>
-          <t>교통비 합계</t>
-        </is>
-      </c>
-      <c r="B40" s="57" t="n"/>
-      <c r="C40" s="57" t="n"/>
-      <c r="D40" s="57" t="n"/>
-      <c r="E40" s="57" t="n"/>
-      <c r="F40" s="57" t="n"/>
-      <c r="G40" s="58">
-        <f>SUM(G5:G39)</f>
-        <v/>
-      </c>
-      <c r="H40" s="57" t="n"/>
-      <c r="I40" s="57" t="n"/>
+      <c r="A40" s="37" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="38">
-      <c r="A41" s="37" t="inlineStr">
-        <is>
-          <t>택시 구간: 즈바리 · 주타 · 게하르트 · 노라방크 · 타테브 · 아부다비 10/4 시내 이동. 아테네(X95)·아부다비(A2) 새벽 공항행은 24시간 공항버스로 해결했습니다.</t>
+      <c r="A41" s="49" t="inlineStr">
+        <is>
+          <t>아부다비 10/4는 루브르(사디야트, 북쪽)와 모스크(알 마크타, 남쪽)가 정반대 방향이라 전 구간 택시로 잡았습니다. 루브르→모스크만 94번 버스로 바꾸면 75→2디르함이지만 60~75분이 걸립니다.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="38">
-      <c r="A42" s="49" t="inlineStr">
-        <is>
-          <t>아부다비 10/4는 루브르(사디야트, 북쪽)와 모스크(알 마크타, 남쪽)가 정반대 방향이라 전 구간 택시로 잡았습니다. 루브르→모스크만 94번 버스로 바꾸면 75→2디르함이지만 60~75분이 걸립니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="38">
-      <c r="A43" s="49" t="inlineStr">
-        <is>
-          <t>아부다비 10/4는 루브르(사디야트, 북쪽)와 모스크(알 마크타, 남쪽)가 정반대 방향이라 전 구간 택시로 잡았습니다. 루브르→모스크만 94번 버스로 바꾸면 75→2디르함이지만 60~75분이 걸립니다.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A42" s="49" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="38"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2615,7 +2550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="37" min="1" max="1"/>
@@ -2929,16 +2864,16 @@
     <row r="13" ht="15" customHeight="1" s="38">
       <c r="A13" s="45" t="inlineStr">
         <is>
-          <t>10/2</t>
+          <t>9/30</t>
         </is>
       </c>
       <c r="B13" s="41" t="inlineStr">
         <is>
-          <t>세바나방크</t>
+          <t>가르니 신전</t>
         </is>
       </c>
       <c r="C13" s="54" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="D13" s="45" t="inlineStr">
         <is>
@@ -2951,7 +2886,7 @@
       </c>
       <c r="F13" s="47" t="inlineStr">
         <is>
-          <t>무료</t>
+          <t>돌의 교향곡은 무료</t>
         </is>
       </c>
     </row>
@@ -2963,11 +2898,11 @@
       </c>
       <c r="B14" s="41" t="inlineStr">
         <is>
-          <t>가르니 신전</t>
+          <t>게하르트 수도원</t>
         </is>
       </c>
       <c r="C14" s="54" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="D14" s="45" t="inlineStr">
         <is>
@@ -2980,23 +2915,23 @@
       </c>
       <c r="F14" s="47" t="inlineStr">
         <is>
-          <t>돌의 교향곡은 무료</t>
+          <t>무료</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="38">
       <c r="A15" s="45" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/1</t>
         </is>
       </c>
       <c r="B15" s="41" t="inlineStr">
         <is>
-          <t>게하르트 수도원</t>
+          <t>에치미아진 보물관</t>
         </is>
       </c>
       <c r="C15" s="54" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="D15" s="45" t="inlineStr">
         <is>
@@ -3009,23 +2944,23 @@
       </c>
       <c r="F15" s="47" t="inlineStr">
         <is>
-          <t>무료</t>
+          <t>대성당 자체는 무료</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="38">
       <c r="A16" s="45" t="inlineStr">
         <is>
-          <t>10/1</t>
+          <t>9/29</t>
         </is>
       </c>
       <c r="B16" s="41" t="inlineStr">
         <is>
-          <t>에치미아진 보물관</t>
+          <t>코르 비랍</t>
         </is>
       </c>
       <c r="C16" s="54" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="D16" s="45" t="inlineStr">
         <is>
@@ -3038,36 +2973,36 @@
       </c>
       <c r="F16" s="47" t="inlineStr">
         <is>
-          <t>대성당 자체는 무료</t>
+          <t>무료 · 투어 포함</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="38">
       <c r="A17" s="45" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/3</t>
         </is>
       </c>
       <c r="B17" s="41" t="inlineStr">
         <is>
-          <t>코르 비랍</t>
+          <t>아크로폴리스</t>
         </is>
       </c>
       <c r="C17" s="54" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E17" s="48">
-        <f>ROUND(C17*환율!$B$5,0)</f>
+        <f>ROUND(C17*환율!$B$6,0)</f>
         <v/>
       </c>
       <c r="F17" s="47" t="inlineStr">
         <is>
-          <t>무료</t>
+          <t>hhticket.gr 공식 정가 30유로(연중 동일) · 타임드 엔트리 필수 · 60일 전 오픈, 성수기 5~7일 전 매진</t>
         </is>
       </c>
     </row>
@@ -3079,11 +3014,11 @@
       </c>
       <c r="B18" s="41" t="inlineStr">
         <is>
-          <t>아크로폴리스</t>
+          <t>고대 아고라 · 헤파이스토스 신전</t>
         </is>
       </c>
       <c r="C18" s="54" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D18" s="45" t="inlineStr">
         <is>
@@ -3096,7 +3031,7 @@
       </c>
       <c r="F18" s="47" t="inlineStr">
         <is>
-          <t>hhticket.gr 공식 정가 30유로(연중 동일) · 타임드 엔트리 필수 · 60일 전 오픈, 성수기 5~7일 전 매진</t>
+          <t>통합권 폐지로 별도 구매 필요 — 현장 확인</t>
         </is>
       </c>
     </row>
@@ -3108,11 +3043,11 @@
       </c>
       <c r="B19" s="41" t="inlineStr">
         <is>
-          <t>고대 아고라 · 헤파이스토스 신전</t>
+          <t>아크로폴리스 박물관</t>
         </is>
       </c>
       <c r="C19" s="54" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D19" s="45" t="inlineStr">
         <is>
@@ -3125,36 +3060,36 @@
       </c>
       <c r="F19" s="47" t="inlineStr">
         <is>
-          <t>통합권 폐지로 별도 구매 필요 — 현장 확인</t>
+          <t>실제 확인가 (별도 티켓)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="38">
       <c r="A20" s="45" t="inlineStr">
         <is>
-          <t>10/3</t>
+          <t>10/4</t>
         </is>
       </c>
       <c r="B20" s="41" t="inlineStr">
         <is>
-          <t>아크로폴리스 박물관</t>
+          <t>루브르 아부다비</t>
         </is>
       </c>
       <c r="C20" s="54" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="D20" s="45" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="E20" s="48">
-        <f>ROUND(C20*환율!$B$6,0)</f>
+        <f>ROUND(C20*환율!$B$7,0)</f>
         <v/>
       </c>
       <c r="F20" s="47" t="inlineStr">
         <is>
-          <t>실제 확인가 (별도 티켓)</t>
+          <t>10/4 일요일 10:00~20:30, 최종 입장 20:00 · 월요일 휴관 · 돔은 자정까지</t>
         </is>
       </c>
     </row>
@@ -3166,11 +3101,11 @@
       </c>
       <c r="B21" s="41" t="inlineStr">
         <is>
-          <t>루브르 아부다비</t>
+          <t>셰이크 자이드 그랜드 모스크</t>
         </is>
       </c>
       <c r="C21" s="54" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D21" s="45" t="inlineStr">
         <is>
@@ -3183,52 +3118,52 @@
       </c>
       <c r="F21" s="47" t="inlineStr">
         <is>
-          <t>10/4 일요일 10:00~20:30, 최종 입장 20:00 · 월요일 휴관 · 돔은 자정까지</t>
+          <t>무료</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="38">
       <c r="A22" s="45" t="inlineStr">
         <is>
-          <t>10/4</t>
+          <t>9/27</t>
         </is>
       </c>
       <c r="B22" s="41" t="inlineStr">
         <is>
-          <t>셰이크 자이드 그랜드 모스크</t>
+          <t>지토그흐치안 도시생활박물관 (귬리)</t>
         </is>
       </c>
       <c r="C22" s="54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D22" s="45" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="E22" s="48">
-        <f>ROUND(C22*환율!$B$7,0)</f>
+        <f>ROUND(C22*환율!$B$5,0)</f>
         <v/>
       </c>
       <c r="F22" s="47" t="inlineStr">
         <is>
-          <t>무료</t>
+          <t>화~금 10:00~17:00 · 일요일 개관 여부 현지 확인</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="38">
       <c r="A23" s="45" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>10/2</t>
         </is>
       </c>
       <c r="B23" s="41" t="inlineStr">
         <is>
-          <t>지토그흐치안 도시생활박물관 (귬리)</t>
+          <t>마테나다란 고문서관</t>
         </is>
       </c>
       <c r="C23" s="54" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D23" s="45" t="inlineStr">
         <is>
@@ -3241,23 +3176,23 @@
       </c>
       <c r="F23" s="47" t="inlineStr">
         <is>
-          <t>화~금 10:00~17:00 · 일요일 개관 여부 현지 확인</t>
+          <t>화~토 10:00~17:50 · 금요일 개관</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="38">
       <c r="A24" s="45" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/2</t>
         </is>
       </c>
       <c r="B24" s="41" t="inlineStr">
         <is>
-          <t>마테나다란 고문서관</t>
+          <t>카페시안 미술관</t>
         </is>
       </c>
       <c r="C24" s="54" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="D24" s="45" t="inlineStr">
         <is>
@@ -3270,19 +3205,19 @@
       </c>
       <c r="F24" s="47" t="inlineStr">
         <is>
-          <t>화~토 10:00~17:50 · 일·월 휴관</t>
+          <t>기부제 · 금~일 20:00까지</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="38">
       <c r="A25" s="45" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/1</t>
         </is>
       </c>
       <c r="B25" s="41" t="inlineStr">
         <is>
-          <t>카페시안 미술관</t>
+          <t>성 흐립시메 교회</t>
         </is>
       </c>
       <c r="C25" s="54" t="n">
@@ -3299,7 +3234,7 @@
       </c>
       <c r="F25" s="47" t="inlineStr">
         <is>
-          <t>기부제 · 월요일 휴관</t>
+          <t>무료 · 유네스코</t>
         </is>
       </c>
     </row>
@@ -3311,11 +3246,11 @@
       </c>
       <c r="B26" s="41" t="inlineStr">
         <is>
-          <t>성 흐립시메 교회</t>
+          <t>즈바르트노츠 유적</t>
         </is>
       </c>
       <c r="C26" s="54" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="D26" s="45" t="inlineStr">
         <is>
@@ -3328,7 +3263,7 @@
       </c>
       <c r="F26" s="47" t="inlineStr">
         <is>
-          <t>무료 · 유네스코</t>
+          <t>7세기 원형 성당 터</t>
         </is>
       </c>
     </row>
@@ -3340,11 +3275,11 @@
       </c>
       <c r="B27" s="41" t="inlineStr">
         <is>
-          <t>즈바르트노츠 유적</t>
+          <t>대학살 추모관 박물관</t>
         </is>
       </c>
       <c r="C27" s="54" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="D27" s="45" t="inlineStr">
         <is>
@@ -3357,19 +3292,19 @@
       </c>
       <c r="F27" s="47" t="inlineStr">
         <is>
-          <t>7세기 원형 성당 터</t>
+          <t>무료 · 17:00 마감 · 월요일 휴관</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="38">
       <c r="A28" s="45" t="inlineStr">
         <is>
-          <t>10/1</t>
+          <t>9/29</t>
         </is>
       </c>
       <c r="B28" s="41" t="inlineStr">
         <is>
-          <t>대학살 추모관 박물관</t>
+          <t>노라방크</t>
         </is>
       </c>
       <c r="C28" s="54" t="n">
@@ -3386,28 +3321,86 @@
       </c>
       <c r="F28" s="47" t="inlineStr">
         <is>
-          <t>무료 · 17:00 마감 · 월요일 휴관</t>
+          <t>무료 · 투어 포함</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="57" t="n"/>
-      <c r="B29" s="56" t="inlineStr">
+      <c r="A29" s="45" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+      <c r="B29" s="41" t="inlineStr">
+        <is>
+          <t>윙스 오브 타테브 케이블카</t>
+        </is>
+      </c>
+      <c r="C29" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="45" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="E29" s="48">
+        <f>ROUND(C29*환율!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="F29" s="47" t="inlineStr">
+        <is>
+          <t>투어 요금에 포함 (개별 구매 시 8,000드람) · 월요일 휴무</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="45" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+      <c r="B30" s="41" t="inlineStr">
+        <is>
+          <t>타테브 수도원</t>
+        </is>
+      </c>
+      <c r="C30" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="45" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="E30" s="48">
+        <f>ROUND(C30*환율!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="F30" s="47" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="57" t="n"/>
+      <c r="B31" s="56" t="inlineStr">
         <is>
           <t>입장료 합계</t>
         </is>
       </c>
-      <c r="C29" s="57" t="n"/>
-      <c r="D29" s="57" t="n"/>
-      <c r="E29" s="58">
-        <f>SUM(E4:E28)</f>
-        <v/>
-      </c>
-      <c r="F29" s="57" t="n"/>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="49" t="inlineStr">
+      <c r="C31" s="57" t="n"/>
+      <c r="D31" s="57" t="n"/>
+      <c r="E31" s="58">
+        <f>SUM(E4:E30)</f>
+        <v/>
+      </c>
+      <c r="F31" s="57" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="49" t="inlineStr">
         <is>
           <t>조지아·아르메니아 수도원은 대부분 무료입니다. 지출은 타테브 케이블카·아크로폴리스·루브르에 몰려 있습니다.</t>
         </is>
@@ -3426,7 +3419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="37" min="1" max="1"/>
@@ -3527,7 +3520,7 @@
         </is>
       </c>
       <c r="D5" s="54">
-        <f>SUMIF(입장료!$A$4:$A$28,A5,입장료!$E$4:$E$28)</f>
+        <f>SUMIF(입장료!$A$4:$A$30,A5,입장료!$E$4:$E$30)</f>
         <v/>
       </c>
       <c r="E5" s="54" t="n">
@@ -3540,11 +3533,11 @@
         <v>6000</v>
       </c>
       <c r="H5" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A5,교통상세!$D$5:$D$39,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A5,교통상세!$D$5:$D$38,"시외")</f>
         <v/>
       </c>
       <c r="I5" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A5,교통상세!$D$5:$D$39,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A5,교통상세!$D$5:$D$38,"시내")</f>
         <v/>
       </c>
       <c r="J5" s="48">
@@ -3573,7 +3566,7 @@
         </is>
       </c>
       <c r="D6" s="54">
-        <f>SUMIF(입장료!$A$4:$A$28,A6,입장료!$E$4:$E$28)</f>
+        <f>SUMIF(입장료!$A$4:$A$30,A6,입장료!$E$4:$E$30)</f>
         <v/>
       </c>
       <c r="E6" s="54" t="n">
@@ -3586,11 +3579,11 @@
         <v>0</v>
       </c>
       <c r="H6" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A6,교통상세!$D$5:$D$39,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A6,교통상세!$D$5:$D$38,"시외")</f>
         <v/>
       </c>
       <c r="I6" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A6,교통상세!$D$5:$D$39,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A6,교통상세!$D$5:$D$38,"시내")</f>
         <v/>
       </c>
       <c r="J6" s="48">
@@ -3619,7 +3612,7 @@
         </is>
       </c>
       <c r="D7" s="54">
-        <f>SUMIF(입장료!$A$4:$A$28,A7,입장료!$E$4:$E$28)</f>
+        <f>SUMIF(입장료!$A$4:$A$30,A7,입장료!$E$4:$E$30)</f>
         <v/>
       </c>
       <c r="E7" s="54" t="n">
@@ -3632,11 +3625,11 @@
         <v>6000</v>
       </c>
       <c r="H7" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A7,교통상세!$D$5:$D$39,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A7,교통상세!$D$5:$D$38,"시외")</f>
         <v/>
       </c>
       <c r="I7" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A7,교통상세!$D$5:$D$39,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A7,교통상세!$D$5:$D$38,"시내")</f>
         <v/>
       </c>
       <c r="J7" s="48">
@@ -3665,7 +3658,7 @@
         </is>
       </c>
       <c r="D8" s="54">
-        <f>SUMIF(입장료!$A$4:$A$28,A8,입장료!$E$4:$E$28)</f>
+        <f>SUMIF(입장료!$A$4:$A$30,A8,입장료!$E$4:$E$30)</f>
         <v/>
       </c>
       <c r="E8" s="54" t="n">
@@ -3678,11 +3671,11 @@
         <v>6000</v>
       </c>
       <c r="H8" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A8,교통상세!$D$5:$D$39,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A8,교통상세!$D$5:$D$38,"시외")</f>
         <v/>
       </c>
       <c r="I8" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A8,교통상세!$D$5:$D$39,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A8,교통상세!$D$5:$D$38,"시내")</f>
         <v/>
       </c>
       <c r="J8" s="48">
@@ -3711,7 +3704,7 @@
         </is>
       </c>
       <c r="D9" s="54">
-        <f>SUMIF(입장료!$A$4:$A$28,A9,입장료!$E$4:$E$28)</f>
+        <f>SUMIF(입장료!$A$4:$A$30,A9,입장료!$E$4:$E$30)</f>
         <v/>
       </c>
       <c r="E9" s="54" t="n">
@@ -3724,11 +3717,11 @@
         <v>5000</v>
       </c>
       <c r="H9" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A9,교통상세!$D$5:$D$39,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A9,교통상세!$D$5:$D$38,"시외")</f>
         <v/>
       </c>
       <c r="I9" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A9,교통상세!$D$5:$D$39,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A9,교통상세!$D$5:$D$38,"시내")</f>
         <v/>
       </c>
       <c r="J9" s="48">
@@ -3757,7 +3750,7 @@
         </is>
       </c>
       <c r="D10" s="54">
-        <f>SUMIF(입장료!$A$4:$A$28,A10,입장료!$E$4:$E$28)</f>
+        <f>SUMIF(입장료!$A$4:$A$30,A10,입장료!$E$4:$E$30)</f>
         <v/>
       </c>
       <c r="E10" s="54" t="n">
@@ -3770,11 +3763,11 @@
         <v>5000</v>
       </c>
       <c r="H10" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A10,교통상세!$D$5:$D$39,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A10,교통상세!$D$5:$D$38,"시외")</f>
         <v/>
       </c>
       <c r="I10" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A10,교통상세!$D$5:$D$39,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A10,교통상세!$D$5:$D$38,"시내")</f>
         <v/>
       </c>
       <c r="J10" s="48">
@@ -3803,7 +3796,7 @@
         </is>
       </c>
       <c r="D11" s="54">
-        <f>SUMIF(입장료!$A$4:$A$28,A11,입장료!$E$4:$E$28)</f>
+        <f>SUMIF(입장료!$A$4:$A$30,A11,입장료!$E$4:$E$30)</f>
         <v/>
       </c>
       <c r="E11" s="54" t="n">
@@ -3816,11 +3809,11 @@
         <v>5000</v>
       </c>
       <c r="H11" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A11,교통상세!$D$5:$D$39,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A11,교통상세!$D$5:$D$38,"시외")</f>
         <v/>
       </c>
       <c r="I11" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A11,교통상세!$D$5:$D$39,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A11,교통상세!$D$5:$D$38,"시내")</f>
         <v/>
       </c>
       <c r="J11" s="48">
@@ -3849,7 +3842,7 @@
         </is>
       </c>
       <c r="D12" s="54">
-        <f>SUMIF(입장료!$A$4:$A$28,A12,입장료!$E$4:$E$28)</f>
+        <f>SUMIF(입장료!$A$4:$A$30,A12,입장료!$E$4:$E$30)</f>
         <v/>
       </c>
       <c r="E12" s="54" t="n">
@@ -3862,11 +3855,11 @@
         <v>5000</v>
       </c>
       <c r="H12" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A12,교통상세!$D$5:$D$39,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A12,교통상세!$D$5:$D$38,"시외")</f>
         <v/>
       </c>
       <c r="I12" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A12,교통상세!$D$5:$D$39,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A12,교통상세!$D$5:$D$38,"시내")</f>
         <v/>
       </c>
       <c r="J12" s="48">
@@ -3895,7 +3888,7 @@
         </is>
       </c>
       <c r="D13" s="54">
-        <f>SUMIF(입장료!$A$4:$A$28,A13,입장료!$E$4:$E$28)</f>
+        <f>SUMIF(입장료!$A$4:$A$30,A13,입장료!$E$4:$E$30)</f>
         <v/>
       </c>
       <c r="E13" s="54" t="n">
@@ -3908,11 +3901,11 @@
         <v>5000</v>
       </c>
       <c r="H13" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A13,교통상세!$D$5:$D$39,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A13,교통상세!$D$5:$D$38,"시외")</f>
         <v/>
       </c>
       <c r="I13" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A13,교통상세!$D$5:$D$39,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A13,교통상세!$D$5:$D$38,"시내")</f>
         <v/>
       </c>
       <c r="J13" s="48">
@@ -3941,7 +3934,7 @@
         </is>
       </c>
       <c r="D14" s="54">
-        <f>SUMIF(입장료!$A$4:$A$28,A14,입장료!$E$4:$E$28)</f>
+        <f>SUMIF(입장료!$A$4:$A$30,A14,입장료!$E$4:$E$30)</f>
         <v/>
       </c>
       <c r="E14" s="54" t="n">
@@ -3954,11 +3947,11 @@
         <v>6000</v>
       </c>
       <c r="H14" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A14,교통상세!$D$5:$D$39,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A14,교통상세!$D$5:$D$38,"시외")</f>
         <v/>
       </c>
       <c r="I14" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A14,교통상세!$D$5:$D$39,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A14,교통상세!$D$5:$D$38,"시내")</f>
         <v/>
       </c>
       <c r="J14" s="48">
@@ -3983,15 +3976,15 @@
       </c>
       <c r="C15" s="66" t="inlineStr">
         <is>
-          <t>예레반 — 코르 비랍·마테나다란</t>
+          <t>예레반 — 타테브 1일 투어</t>
         </is>
       </c>
       <c r="D15" s="54">
-        <f>SUMIF(입장료!$A$4:$A$28,A15,입장료!$E$4:$E$28)</f>
+        <f>SUMIF(입장료!$A$4:$A$30,A15,입장료!$E$4:$E$30)</f>
         <v/>
       </c>
       <c r="E15" s="54" t="n">
-        <v>30000</v>
+        <v>35000</v>
       </c>
       <c r="F15" s="54" t="n">
         <v>20000</v>
@@ -4000,11 +3993,11 @@
         <v>6000</v>
       </c>
       <c r="H15" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A15,교통상세!$D$5:$D$39,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A15,교통상세!$D$5:$D$38,"시외")</f>
         <v/>
       </c>
       <c r="I15" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A15,교통상세!$D$5:$D$39,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A15,교통상세!$D$5:$D$38,"시내")</f>
         <v/>
       </c>
       <c r="J15" s="48">
@@ -4033,7 +4026,7 @@
         </is>
       </c>
       <c r="D16" s="54">
-        <f>SUMIF(입장료!$A$4:$A$28,A16,입장료!$E$4:$E$28)</f>
+        <f>SUMIF(입장료!$A$4:$A$30,A16,입장료!$E$4:$E$30)</f>
         <v/>
       </c>
       <c r="E16" s="54" t="n">
@@ -4046,11 +4039,11 @@
         <v>5000</v>
       </c>
       <c r="H16" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A16,교통상세!$D$5:$D$39,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A16,교통상세!$D$5:$D$38,"시외")</f>
         <v/>
       </c>
       <c r="I16" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A16,교통상세!$D$5:$D$39,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A16,교통상세!$D$5:$D$38,"시내")</f>
         <v/>
       </c>
       <c r="J16" s="48">
@@ -4079,7 +4072,7 @@
         </is>
       </c>
       <c r="D17" s="54">
-        <f>SUMIF(입장료!$A$4:$A$28,A17,입장료!$E$4:$E$28)</f>
+        <f>SUMIF(입장료!$A$4:$A$30,A17,입장료!$E$4:$E$30)</f>
         <v/>
       </c>
       <c r="E17" s="54" t="n">
@@ -4092,11 +4085,11 @@
         <v>5000</v>
       </c>
       <c r="H17" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A17,교통상세!$D$5:$D$39,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A17,교통상세!$D$5:$D$38,"시외")</f>
         <v/>
       </c>
       <c r="I17" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A17,교통상세!$D$5:$D$39,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A17,교통상세!$D$5:$D$38,"시내")</f>
         <v/>
       </c>
       <c r="J17" s="48">
@@ -4121,11 +4114,11 @@
       </c>
       <c r="C18" s="66" t="inlineStr">
         <is>
-          <t>예레반 — 세반 호수 당일치기</t>
+          <t>예레반 — 마테나다란·도심 도보</t>
         </is>
       </c>
       <c r="D18" s="54">
-        <f>SUMIF(입장료!$A$4:$A$28,A18,입장료!$E$4:$E$28)</f>
+        <f>SUMIF(입장료!$A$4:$A$30,A18,입장료!$E$4:$E$30)</f>
         <v/>
       </c>
       <c r="E18" s="54" t="n">
@@ -4138,11 +4131,11 @@
         <v>6000</v>
       </c>
       <c r="H18" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A18,교통상세!$D$5:$D$39,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A18,교통상세!$D$5:$D$38,"시외")</f>
         <v/>
       </c>
       <c r="I18" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A18,교통상세!$D$5:$D$39,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A18,교통상세!$D$5:$D$38,"시내")</f>
         <v/>
       </c>
       <c r="J18" s="48">
@@ -4171,7 +4164,7 @@
         </is>
       </c>
       <c r="D19" s="54">
-        <f>SUMIF(입장료!$A$4:$A$28,A19,입장료!$E$4:$E$28)</f>
+        <f>SUMIF(입장료!$A$4:$A$30,A19,입장료!$E$4:$E$30)</f>
         <v/>
       </c>
       <c r="E19" s="54" t="n">
@@ -4184,11 +4177,11 @@
         <v>8000</v>
       </c>
       <c r="H19" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A19,교통상세!$D$5:$D$39,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A19,교통상세!$D$5:$D$38,"시외")</f>
         <v/>
       </c>
       <c r="I19" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A19,교통상세!$D$5:$D$39,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A19,교통상세!$D$5:$D$38,"시내")</f>
         <v/>
       </c>
       <c r="J19" s="48">
@@ -4217,7 +4210,7 @@
         </is>
       </c>
       <c r="D20" s="54">
-        <f>SUMIF(입장료!$A$4:$A$28,A20,입장료!$E$4:$E$28)</f>
+        <f>SUMIF(입장료!$A$4:$A$30,A20,입장료!$E$4:$E$30)</f>
         <v/>
       </c>
       <c r="E20" s="54" t="n">
@@ -4230,11 +4223,11 @@
         <v>8000</v>
       </c>
       <c r="H20" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A20,교통상세!$D$5:$D$39,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A20,교통상세!$D$5:$D$38,"시외")</f>
         <v/>
       </c>
       <c r="I20" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A20,교통상세!$D$5:$D$39,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A20,교통상세!$D$5:$D$38,"시내")</f>
         <v/>
       </c>
       <c r="J20" s="48">
@@ -4263,7 +4256,7 @@
         </is>
       </c>
       <c r="D21" s="54">
-        <f>SUMIF(입장료!$A$4:$A$28,A21,입장료!$E$4:$E$28)</f>
+        <f>SUMIF(입장료!$A$4:$A$30,A21,입장료!$E$4:$E$30)</f>
         <v/>
       </c>
       <c r="E21" s="54" t="n">
@@ -4276,11 +4269,11 @@
         <v>0</v>
       </c>
       <c r="H21" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A21,교통상세!$D$5:$D$39,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A21,교통상세!$D$5:$D$38,"시외")</f>
         <v/>
       </c>
       <c r="I21" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$39,교통상세!$A$5:$A$39,A21,교통상세!$D$5:$D$39,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A21,교통상세!$D$5:$D$38,"시내")</f>
         <v/>
       </c>
       <c r="J21" s="48">
@@ -4436,6 +4429,21 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/여행예산_상하이반영.xlsx
+++ b/여행예산_상하이반영.xlsx
@@ -925,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="37" min="1" max="1"/>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="B15" s="41" t="inlineStr">
         <is>
-          <t>트빌리시 시내 (디두베 → 숙소)</t>
+          <t>트빌리시 시내 (디두베 → 오르타찰라)</t>
         </is>
       </c>
       <c r="C15" s="41" t="inlineStr">
@@ -1480,14 +1480,14 @@
       </c>
       <c r="I15" s="47" t="inlineStr">
         <is>
-          <t>지하철</t>
+          <t>지하철 + 도보</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="38">
       <c r="A16" s="45" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>9/27</t>
         </is>
       </c>
       <c r="B16" s="41" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="17" ht="15" customHeight="1" s="38">
       <c r="A17" s="45" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>9/27</t>
         </is>
       </c>
       <c r="B17" s="41" t="inlineStr">
@@ -1575,7 +1575,7 @@
     <row r="18" ht="15" customHeight="1" s="38">
       <c r="A18" s="45" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>9/27</t>
         </is>
       </c>
       <c r="B18" s="41" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="19" ht="15" customHeight="1" s="38">
       <c r="A19" s="45" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>9/28</t>
         </is>
       </c>
       <c r="B19" s="41" t="inlineStr">
@@ -1663,17 +1663,17 @@
     <row r="20" ht="15" customHeight="1" s="38">
       <c r="A20" s="45" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>9/29</t>
         </is>
       </c>
       <c r="B20" s="41" t="inlineStr">
         <is>
-          <t>바나조르 → 귬리</t>
+          <t>예레반 → 코르 비랍 · 노라방크 · 타테브 (왕복)</t>
         </is>
       </c>
       <c r="C20" s="41" t="inlineStr">
         <is>
-          <t>마르슈르트카</t>
+          <t>1일 그룹투어 (미니버스)</t>
         </is>
       </c>
       <c r="D20" s="53" t="inlineStr">
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="E20" s="54" t="n">
-        <v>1500</v>
+        <v>25000</v>
       </c>
       <c r="F20" s="45" t="inlineStr">
         <is>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="H20" s="55" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="I20" s="47" t="inlineStr">
         <is>
-          <t>스피타크 경유 1시간 40분 · 1,000~1,500드람</t>
+          <t>Hyur Service 63.72달러 · 입장료·케이블카 포함, 점심 별도 · 08:30~22:30</t>
         </is>
       </c>
     </row>
@@ -1712,21 +1712,21 @@
       </c>
       <c r="B21" s="41" t="inlineStr">
         <is>
-          <t>귬리 → 예레반</t>
+          <t>킬리키아 터미널 → 시내</t>
         </is>
       </c>
       <c r="C21" s="41" t="inlineStr">
         <is>
-          <t>마르슈르트카</t>
+          <t>버스</t>
         </is>
       </c>
       <c r="D21" s="53" t="inlineStr">
         <is>
-          <t>시외</t>
+          <t>시내</t>
         </is>
       </c>
       <c r="E21" s="54" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="F21" s="45" t="inlineStr">
         <is>
@@ -1744,33 +1744,33 @@
       </c>
       <c r="I21" s="47" t="inlineStr">
         <is>
-          <t>2시간 · 수시 출발 · 급행 전동열차도 비슷한 값</t>
+          <t>또는 얀덱스 택시</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="38">
       <c r="A22" s="45" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>9/30</t>
         </is>
       </c>
       <c r="B22" s="41" t="inlineStr">
         <is>
-          <t>예레반 → 코르 비랍 · 노라방크 · 타테브 (왕복)</t>
+          <t>가르니 → 게하르트 왕복</t>
         </is>
       </c>
       <c r="C22" s="41" t="inlineStr">
         <is>
-          <t>1일 그룹투어 (미니버스)</t>
+          <t>택시</t>
         </is>
       </c>
       <c r="D22" s="53" t="inlineStr">
         <is>
-          <t>시외</t>
+          <t>시내</t>
         </is>
       </c>
       <c r="E22" s="54" t="n">
-        <v>25000</v>
+        <v>3000</v>
       </c>
       <c r="F22" s="45" t="inlineStr">
         <is>
@@ -1788,24 +1788,24 @@
       </c>
       <c r="I22" s="47" t="inlineStr">
         <is>
-          <t>Hyur Service 63.72달러 · 입장료·케이블카 포함, 점심 별도 · 08:30~22:30</t>
+          <t>9km, 대중교통 없음 · 1인 단독이라 전액 부담</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="38">
       <c r="A23" s="45" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>10/1</t>
         </is>
       </c>
       <c r="B23" s="41" t="inlineStr">
         <is>
-          <t>킬리키아 터미널 → 시내</t>
+          <t>예레반 → 에치미아진 왕복</t>
         </is>
       </c>
       <c r="C23" s="41" t="inlineStr">
         <is>
-          <t>버스</t>
+          <t>마르슈르트카</t>
         </is>
       </c>
       <c r="D23" s="53" t="inlineStr">
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="E23" s="54" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F23" s="45" t="inlineStr">
         <is>
@@ -1832,19 +1832,19 @@
       </c>
       <c r="I23" s="43" t="inlineStr">
         <is>
-          <t>또는 얀덱스 택시</t>
+          <t>킬리키아 터미널</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="38">
       <c r="A24" s="45" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/3</t>
         </is>
       </c>
       <c r="B24" s="41" t="inlineStr">
         <is>
-          <t>가르니 → 게하르트 왕복</t>
+          <t>예레반 → 즈바르트노츠 공항</t>
         </is>
       </c>
       <c r="C24" s="41" t="inlineStr">
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="E24" s="54" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="F24" s="45" t="inlineStr">
         <is>
@@ -1871,29 +1871,29 @@
       </c>
       <c r="H24" s="55" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>△</t>
         </is>
       </c>
       <c r="I24" s="47" t="inlineStr">
         <is>
-          <t>9km, 대중교통 없음 · 1인 단독이라 전액 부담</t>
+          <t>01:30경 출발, 심야 할증 감안</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="38">
       <c r="A25" s="45" t="inlineStr">
         <is>
-          <t>10/1</t>
+          <t>10/3</t>
         </is>
       </c>
       <c r="B25" s="41" t="inlineStr">
         <is>
-          <t>예레반 → 에치미아진 왕복</t>
+          <t>아테네 공항 → 신타그마역</t>
         </is>
       </c>
       <c r="C25" s="41" t="inlineStr">
         <is>
-          <t>마르슈르트카</t>
+          <t>메트로 3호선</t>
         </is>
       </c>
       <c r="D25" s="53" t="inlineStr">
@@ -1902,15 +1902,15 @@
         </is>
       </c>
       <c r="E25" s="54" t="n">
-        <v>600</v>
+        <v>10</v>
       </c>
       <c r="F25" s="45" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G25" s="48">
-        <f>ROUND(E25*환율!$B$5/1,0)</f>
+        <f>ROUND(E25*환율!$B$6/1,0)</f>
         <v/>
       </c>
       <c r="H25" s="55" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="I25" s="47" t="inlineStr">
         <is>
-          <t>킬리키아 터미널</t>
+          <t>공항선 정액 10유로, 40분</t>
         </is>
       </c>
     </row>
@@ -1932,12 +1932,12 @@
       </c>
       <c r="B26" s="41" t="inlineStr">
         <is>
-          <t>예레반 → 즈바르트노츠 공항</t>
+          <t>아테네 시내 이동</t>
         </is>
       </c>
       <c r="C26" s="41" t="inlineStr">
         <is>
-          <t>택시</t>
+          <t>메트로·트램 4~5회</t>
         </is>
       </c>
       <c r="D26" s="53" t="inlineStr">
@@ -1946,42 +1946,42 @@
         </is>
       </c>
       <c r="E26" s="54" t="n">
-        <v>4000</v>
+        <v>6</v>
       </c>
       <c r="F26" s="45" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G26" s="48">
-        <f>ROUND(E26*환율!$B$5/1,0)</f>
+        <f>ROUND(E26*환율!$B$6/1,0)</f>
         <v/>
       </c>
       <c r="H26" s="55" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>○</t>
         </is>
       </c>
       <c r="I26" s="47" t="inlineStr">
         <is>
-          <t>01:30경 출발, 심야 할증 감안</t>
+          <t>1회 1.20유로. 대부분 도보권이라 보조 수단</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="38">
       <c r="A27" s="45" t="inlineStr">
         <is>
-          <t>10/3</t>
+          <t>10/4</t>
         </is>
       </c>
       <c r="B27" s="41" t="inlineStr">
         <is>
-          <t>아테네 공항 → 신타그마역</t>
+          <t>아테네 → 공항 (04:10 출발)</t>
         </is>
       </c>
       <c r="C27" s="41" t="inlineStr">
         <is>
-          <t>메트로 3호선</t>
+          <t>X95 공항버스</t>
         </is>
       </c>
       <c r="D27" s="53" t="inlineStr">
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="E27" s="54" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="F27" s="45" t="inlineStr">
         <is>
@@ -2008,24 +2008,24 @@
       </c>
       <c r="I27" s="43" t="inlineStr">
         <is>
-          <t>공항선 정액 10유로, 40분</t>
+          <t>신타그마 발 24시간 운행 · 야간 60분 간격이라 03:55까지 정류장 도착 · 승차권은 전날 지하철역에서 미리 구입 · 택시는 심야 정액 55유로</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="38">
       <c r="A28" s="45" t="inlineStr">
         <is>
-          <t>10/3</t>
+          <t>10/4</t>
         </is>
       </c>
       <c r="B28" s="41" t="inlineStr">
         <is>
-          <t>아테네 시내 이동</t>
+          <t>자이드 국제공항 → TRYP 호텔</t>
         </is>
       </c>
       <c r="C28" s="41" t="inlineStr">
         <is>
-          <t>메트로·트램 4~5회</t>
+          <t>택시</t>
         </is>
       </c>
       <c r="D28" s="53" t="inlineStr">
@@ -2034,25 +2034,25 @@
         </is>
       </c>
       <c r="E28" s="54" t="n">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="F28" s="45" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="G28" s="48">
-        <f>ROUND(E28*환율!$B$6/1,0)</f>
+        <f>ROUND(E28*환율!$B$7/1,0)</f>
         <v/>
       </c>
       <c r="H28" s="55" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="I28" s="47" t="inlineStr">
         <is>
-          <t>1회 1.20유로. 대부분 도보권이라 보조 수단</t>
+          <t>칼리파 bin 자이드 St · 30~40분 · 미터 약 85~100디르함</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2064,12 @@
       </c>
       <c r="B29" s="41" t="inlineStr">
         <is>
-          <t>아테네 → 공항 (04:10 출발)</t>
+          <t>TRYP 호텔 → 루브르 아부다비</t>
         </is>
       </c>
       <c r="C29" s="41" t="inlineStr">
         <is>
-          <t>X95 공항버스</t>
+          <t>택시</t>
         </is>
       </c>
       <c r="D29" s="53" t="inlineStr">
@@ -2078,25 +2078,25 @@
         </is>
       </c>
       <c r="E29" s="54" t="n">
-        <v>6.2</v>
+        <v>45</v>
       </c>
       <c r="F29" s="45" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="G29" s="48">
-        <f>ROUND(E29*환율!$B$6/1,0)</f>
+        <f>ROUND(E29*환율!$B$7/1,0)</f>
         <v/>
       </c>
       <c r="H29" s="55" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="I29" s="43" t="inlineStr">
         <is>
-          <t>신타그마 발 24시간 운행 · 야간 60분 간격이라 03:55까지 정류장 도착 · 승차권은 전날 지하철역에서 미리 구입 · 택시는 심야 정액 55유로</t>
+          <t>사디야트 섬 · 약 14km, 20~25분</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="B30" s="41" t="inlineStr">
         <is>
-          <t>자이드 국제공항 → TRYP 호텔</t>
+          <t>루브르 → 셰이크 자이드 모스크</t>
         </is>
       </c>
       <c r="C30" s="41" t="inlineStr">
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="E30" s="54" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="F30" s="45" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I30" s="47" t="inlineStr">
         <is>
-          <t>칼리파 bin 자이드 St · 30~40분 · 미터 약 85~100디르함</t>
+          <t>섬 반대편 횡단 약 28km, 30~35분 · 94번 버스면 2디르함이나 60~75분</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B31" s="41" t="inlineStr">
         <is>
-          <t>TRYP 호텔 → 루브르 아부다비</t>
+          <t>모스크 → TRYP 호텔</t>
         </is>
       </c>
       <c r="C31" s="41" t="inlineStr">
@@ -2184,24 +2184,24 @@
       </c>
       <c r="I31" s="43" t="inlineStr">
         <is>
-          <t>사디야트 섬 · 약 14km, 20~25분</t>
+          <t>약 14km, 18~20분</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="38">
       <c r="A32" s="45" t="inlineStr">
         <is>
-          <t>10/4</t>
+          <t>10/5</t>
         </is>
       </c>
       <c r="B32" s="41" t="inlineStr">
         <is>
-          <t>루브르 → 셰이크 자이드 모스크</t>
+          <t>TRYP 호텔 → 공항 (05:30)</t>
         </is>
       </c>
       <c r="C32" s="41" t="inlineStr">
         <is>
-          <t>택시</t>
+          <t>A2 공항버스</t>
         </is>
       </c>
       <c r="D32" s="53" t="inlineStr">
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="E32" s="54" t="n">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="F32" s="45" t="inlineStr">
         <is>
@@ -2223,73 +2223,73 @@
       </c>
       <c r="H32" s="55" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>○</t>
         </is>
       </c>
       <c r="I32" s="47" t="inlineStr">
         <is>
-          <t>섬 반대편 횡단 약 28km, 30~35분 · 94번 버스면 2디르함이나 60~75분</t>
+          <t>버스 4디르함 + 하필라트 카드 10디르함 · 칼리파 bin 자이드 St 승차 · 40~45분</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="38">
       <c r="A33" s="45" t="inlineStr">
         <is>
-          <t>10/4</t>
+          <t>9/30</t>
         </is>
       </c>
       <c r="B33" s="41" t="inlineStr">
         <is>
-          <t>모스크 → TRYP 호텔</t>
+          <t>예레반 → 가르니 왕복</t>
         </is>
       </c>
       <c r="C33" s="41" t="inlineStr">
         <is>
-          <t>택시</t>
+          <t>266·284번 버스</t>
         </is>
       </c>
       <c r="D33" s="53" t="inlineStr">
         <is>
-          <t>시내</t>
+          <t>시외</t>
         </is>
       </c>
       <c r="E33" s="54" t="n">
-        <v>45</v>
+        <v>500</v>
       </c>
       <c r="F33" s="45" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="G33" s="48">
-        <f>ROUND(E33*환율!$B$7/1,0)</f>
+        <f>ROUND(E33*환율!$B$5/1,0)</f>
         <v/>
       </c>
       <c r="H33" s="55" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>○</t>
         </is>
       </c>
       <c r="I33" s="43" t="inlineStr">
         <is>
-          <t>약 14km, 18~20분</t>
+          <t>가이 정류장 출발 · 30분 간격 · 왕복 500드람</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="38">
       <c r="A34" s="45" t="inlineStr">
         <is>
-          <t>10/5</t>
+          <t>9/24</t>
         </is>
       </c>
       <c r="B34" s="41" t="inlineStr">
         <is>
-          <t>TRYP 호텔 → 공항 (05:30)</t>
+          <t>스테판츠민다 → 주타 왕복</t>
         </is>
       </c>
       <c r="C34" s="41" t="inlineStr">
         <is>
-          <t>A2 공항버스</t>
+          <t>4WD 택시 (대기 포함)</t>
         </is>
       </c>
       <c r="D34" s="53" t="inlineStr">
@@ -2298,51 +2298,51 @@
         </is>
       </c>
       <c r="E34" s="54" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="F34" s="45" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="G34" s="48">
-        <f>ROUND(E34*환율!$B$7/1,0)</f>
+        <f>ROUND(E34*환율!$B$4/1,0)</f>
         <v/>
       </c>
       <c r="H34" s="55" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="I34" s="47" t="inlineStr">
         <is>
-          <t>버스 4디르함 + 하필라트 카드 10디르함 · 칼리파 bin 자이드 St 승차 · 40~45분</t>
+          <t>대중교통 없음 · 25km 비포장 · 1인 단독이면 전액. 동행 구하면 40라리</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="38">
       <c r="A35" s="45" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>9/29</t>
         </is>
       </c>
       <c r="B35" s="41" t="inlineStr">
         <is>
-          <t>예레반 → 가르니 왕복</t>
+          <t>투어 사무실 → 숙소 (심야)</t>
         </is>
       </c>
       <c r="C35" s="41" t="inlineStr">
         <is>
-          <t>266·284번 버스</t>
+          <t>택시 또는 도보</t>
         </is>
       </c>
       <c r="D35" s="53" t="inlineStr">
         <is>
-          <t>시외</t>
+          <t>시내</t>
         </is>
       </c>
       <c r="E35" s="54" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F35" s="45" t="inlineStr">
         <is>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="H35" s="55" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>△</t>
         </is>
       </c>
       <c r="I35" s="43" t="inlineStr">
         <is>
-          <t>가이 정류장 출발 · 30분 간격 · 왕복 500드람</t>
+          <t>22:30 이후 날반댠 96번지 하차 · 도보 10분이면 0원</t>
         </is>
       </c>
     </row>
@@ -2372,21 +2372,21 @@
       </c>
       <c r="B36" s="41" t="inlineStr">
         <is>
-          <t>스테판츠민다 → 주타 왕복</t>
+          <t>오르타찰라 → 주그디디 (야간버스)</t>
         </is>
       </c>
       <c r="C36" s="41" t="inlineStr">
         <is>
-          <t>4WD 택시 (대기 포함)</t>
+          <t>OmniBus</t>
         </is>
       </c>
       <c r="D36" s="53" t="inlineStr">
         <is>
-          <t>시내</t>
+          <t>시외</t>
         </is>
       </c>
       <c r="E36" s="54" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F36" s="45" t="inlineStr">
         <is>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="H36" s="55" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>○</t>
         </is>
       </c>
       <c r="I36" s="47" t="inlineStr">
         <is>
-          <t>대중교통 없음 · 25km 비포장 · 1인 단독이면 전액. 동행 구하면 40라리</t>
+          <t>자정 발 · 약 5시간 20분 · 운행 불확실 — tkt.ge 사전 확인 필수</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B37" s="41" t="inlineStr">
         <is>
-          <t>트빌리시 → 시그나기 왕복</t>
+          <t>주그디디 → 메스티아</t>
         </is>
       </c>
       <c r="C37" s="41" t="inlineStr">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="E37" s="54" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F37" s="45" t="inlineStr">
         <is>
@@ -2448,24 +2448,24 @@
       </c>
       <c r="I37" s="47" t="inlineStr">
         <is>
-          <t>삼고리 터미널 출발 · 편도 2~2.5시간 · 보드베는 요청하면 하차 · 돌아오는 막차 18~19시</t>
+          <t>15:00 발 · 3~4시간 · 확정 편 하루 한 번뿐</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="38">
       <c r="A38" s="45" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>9/26</t>
         </is>
       </c>
       <c r="B38" s="41" t="inlineStr">
         <is>
-          <t>투어 사무실 → 숙소 (심야)</t>
+          <t>메스티아 → 찰라디 트레일헤드 왕복</t>
         </is>
       </c>
       <c r="C38" s="41" t="inlineStr">
         <is>
-          <t>택시 또는 도보</t>
+          <t>택시 (대기 포함)</t>
         </is>
       </c>
       <c r="D38" s="53" t="inlineStr">
@@ -2474,62 +2474,195 @@
         </is>
       </c>
       <c r="E38" s="54" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="F38" s="45" t="inlineStr">
         <is>
+          <t>GEL</t>
+        </is>
+      </c>
+      <c r="G38" s="48">
+        <f>ROUND(E38*환율!$B$4/1,0)</f>
+        <v/>
+      </c>
+      <c r="H38" s="55" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="I38" s="47" t="inlineStr">
+        <is>
+          <t>10km · 대중교통 없음 · 1인 단독이면 전액</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="38">
+      <c r="A39" s="45" t="inlineStr">
+        <is>
+          <t>9/26</t>
+        </is>
+      </c>
+      <c r="B39" s="41" t="inlineStr">
+        <is>
+          <t>메스티아 → 주그디디</t>
+        </is>
+      </c>
+      <c r="C39" s="41" t="inlineStr">
+        <is>
+          <t>마르슈르트카 또는 셰어택시</t>
+        </is>
+      </c>
+      <c r="D39" s="53" t="inlineStr">
+        <is>
+          <t>시외</t>
+        </is>
+      </c>
+      <c r="E39" s="54" t="n">
+        <v>40</v>
+      </c>
+      <c r="F39" s="45" t="inlineStr">
+        <is>
+          <t>GEL</t>
+        </is>
+      </c>
+      <c r="G39" s="48">
+        <f>ROUND(E39*환율!$B$4/1,0)</f>
+        <v/>
+      </c>
+      <c r="H39" s="55" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="I39" s="43" t="inlineStr">
+        <is>
+          <t>공식 확정편은 08:00뿐 — 오후 편은 성수기 비공식. 숙소에 사전 확보 권장</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="38">
+      <c r="A40" s="45" t="inlineStr">
+        <is>
+          <t>9/26</t>
+        </is>
+      </c>
+      <c r="B40" s="41" t="inlineStr">
+        <is>
+          <t>오르타찰라 → 트빌리시 (야간버스)</t>
+        </is>
+      </c>
+      <c r="C40" s="41" t="inlineStr">
+        <is>
+          <t>OmniBus</t>
+        </is>
+      </c>
+      <c r="D40" s="53" t="inlineStr">
+        <is>
+          <t>시외</t>
+        </is>
+      </c>
+      <c r="E40" s="54" t="n">
+        <v>30</v>
+      </c>
+      <c r="F40" s="45" t="inlineStr">
+        <is>
+          <t>GEL</t>
+        </is>
+      </c>
+      <c r="G40" s="48">
+        <f>ROUND(E40*환율!$B$4/1,0)</f>
+        <v/>
+      </c>
+      <c r="H40" s="55" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I40" s="43" t="inlineStr">
+        <is>
+          <t>주그디디 자정 발 · 약 5시간 20분 · 운행 불확실 — tkt.ge 사전 확인 필수</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="38">
+      <c r="A41" s="45" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+      <c r="B41" s="41" t="inlineStr">
+        <is>
+          <t>바나조르 → 예레반</t>
+        </is>
+      </c>
+      <c r="C41" s="41" t="inlineStr">
+        <is>
+          <t>마르슈르트카</t>
+        </is>
+      </c>
+      <c r="D41" s="53" t="inlineStr">
+        <is>
+          <t>시외</t>
+        </is>
+      </c>
+      <c r="E41" s="54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F41" s="45" t="inlineStr">
+        <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="G38" s="48">
-        <f>ROUND(E38*환율!$B$5/1,0)</f>
-        <v/>
-      </c>
-      <c r="H38" s="55" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="I38" s="47" t="inlineStr">
-        <is>
-          <t>22:30 이후 날반댠 96번지 하차 · 도보 10분이면 0원</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="38">
-      <c r="A39" s="56" t="inlineStr">
+      <c r="G41" s="48">
+        <f>ROUND(E41*환율!$B$5/1,0)</f>
+        <v/>
+      </c>
+      <c r="H41" s="55" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I41" s="43" t="inlineStr">
+        <is>
+          <t>약 2시간 · 수시 출발 · 귬리 경유 시세에 준한 추정치, 현지 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="38">
+      <c r="A42" s="56" t="inlineStr">
         <is>
           <t>교통비 합계</t>
         </is>
       </c>
-      <c r="B39" s="57" t="n"/>
-      <c r="C39" s="57" t="n"/>
-      <c r="D39" s="57" t="n"/>
-      <c r="E39" s="57" t="n"/>
-      <c r="F39" s="57" t="n"/>
-      <c r="G39" s="58">
-        <f>SUM(G5:G38)</f>
-        <v/>
-      </c>
-      <c r="H39" s="57" t="n"/>
-      <c r="I39" s="57" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="38">
-      <c r="A40" s="37" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="38">
-      <c r="A41" s="49" t="inlineStr">
+      <c r="B42" s="57" t="n"/>
+      <c r="C42" s="57" t="n"/>
+      <c r="D42" s="57" t="n"/>
+      <c r="E42" s="57" t="n"/>
+      <c r="F42" s="57" t="n"/>
+      <c r="G42" s="58">
+        <f>SUM(G5:G41)</f>
+        <v/>
+      </c>
+      <c r="H42" s="57" t="n"/>
+      <c r="I42" s="57" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="38">
+      <c r="A43" s="37" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="49" t="inlineStr">
         <is>
           <t>아부다비 10/4는 루브르(사디야트, 북쪽)와 모스크(알 마크타, 남쪽)가 정반대 방향이라 전 구간 택시로 잡았습니다. 루브르→모스크만 94번 버스로 바꾸면 75→2디르함이지만 60~75분이 걸립니다.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="38">
-      <c r="A42" s="49" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="38"/>
-    <row r="44"/>
-    <row r="45"/>
+    <row r="45">
+      <c r="A45" s="49" t="inlineStr">
+        <is>
+          <t>OmniBus 트빌리시↔주그디디 심야편(9/24·9/26, 각 30라리)은 운행 여부가 자료마다 엇갈립니다. 도로공사로 심야 구간이 막혀 있었다는 보고가 있어 tkt.ge에서 사전 확인이 필요하고, 안 되면 주간열차(08:15 발)나 저녁 마르슈르트카로 대체해야 합니다.</t>
+        </is>
+      </c>
+    </row>
     <row r="46"/>
     <row r="47"/>
     <row r="48"/>
@@ -2537,6 +2670,9 @@
     <row r="50"/>
     <row r="51"/>
     <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2806,45 +2942,45 @@
     <row r="11" ht="15" customHeight="1" s="38">
       <c r="A11" s="45" t="inlineStr">
         <is>
-          <t>9/25</t>
+          <t>9/26</t>
         </is>
       </c>
       <c r="B11" s="41" t="inlineStr">
         <is>
-          <t>시그나기 와이너리 시음 (선택)</t>
+          <t>하흐파트 수도원</t>
         </is>
       </c>
       <c r="C11" s="54" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D11" s="45" t="inlineStr">
         <is>
-          <t>GEL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="E11" s="48">
-        <f>ROUND(C11*환율!$B$4,0)</f>
+        <f>ROUND(C11*환율!$B$5,0)</f>
         <v/>
       </c>
       <c r="F11" s="47" t="inlineStr">
         <is>
-          <t>크베브리 오렌지와인. 생략 가능 · 보드베·시그나기 성벽은 무료</t>
+          <t>무료</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="38">
       <c r="A12" s="45" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>9/30</t>
         </is>
       </c>
       <c r="B12" s="41" t="inlineStr">
         <is>
-          <t>하흐파트 수도원</t>
+          <t>가르니 신전</t>
         </is>
       </c>
       <c r="C12" s="54" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="D12" s="45" t="inlineStr">
         <is>
@@ -2857,7 +2993,7 @@
       </c>
       <c r="F12" s="47" t="inlineStr">
         <is>
-          <t>무료</t>
+          <t>돌의 교향곡은 무료</t>
         </is>
       </c>
     </row>
@@ -2869,11 +3005,11 @@
       </c>
       <c r="B13" s="41" t="inlineStr">
         <is>
-          <t>가르니 신전</t>
+          <t>게하르트 수도원</t>
         </is>
       </c>
       <c r="C13" s="54" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="D13" s="45" t="inlineStr">
         <is>
@@ -2886,23 +3022,23 @@
       </c>
       <c r="F13" s="47" t="inlineStr">
         <is>
-          <t>돌의 교향곡은 무료</t>
+          <t>무료</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="38">
       <c r="A14" s="45" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/1</t>
         </is>
       </c>
       <c r="B14" s="41" t="inlineStr">
         <is>
-          <t>게하르트 수도원</t>
+          <t>에치미아진 보물관</t>
         </is>
       </c>
       <c r="C14" s="54" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="D14" s="45" t="inlineStr">
         <is>
@@ -2915,23 +3051,23 @@
       </c>
       <c r="F14" s="47" t="inlineStr">
         <is>
-          <t>무료</t>
+          <t>대성당 자체는 무료</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="38">
       <c r="A15" s="45" t="inlineStr">
         <is>
-          <t>10/1</t>
+          <t>9/29</t>
         </is>
       </c>
       <c r="B15" s="41" t="inlineStr">
         <is>
-          <t>에치미아진 보물관</t>
+          <t>코르 비랍</t>
         </is>
       </c>
       <c r="C15" s="54" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="D15" s="45" t="inlineStr">
         <is>
@@ -2944,36 +3080,36 @@
       </c>
       <c r="F15" s="47" t="inlineStr">
         <is>
-          <t>대성당 자체는 무료</t>
+          <t>무료 · 투어 포함</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="38">
       <c r="A16" s="45" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/3</t>
         </is>
       </c>
       <c r="B16" s="41" t="inlineStr">
         <is>
-          <t>코르 비랍</t>
+          <t>아크로폴리스</t>
         </is>
       </c>
       <c r="C16" s="54" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D16" s="45" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E16" s="48">
-        <f>ROUND(C16*환율!$B$5,0)</f>
+        <f>ROUND(C16*환율!$B$6,0)</f>
         <v/>
       </c>
       <c r="F16" s="47" t="inlineStr">
         <is>
-          <t>무료 · 투어 포함</t>
+          <t>hhticket.gr 공식 정가 30유로(연중 동일) · 타임드 엔트리 필수 · 60일 전 오픈, 성수기 5~7일 전 매진</t>
         </is>
       </c>
     </row>
@@ -2985,11 +3121,11 @@
       </c>
       <c r="B17" s="41" t="inlineStr">
         <is>
-          <t>아크로폴리스</t>
+          <t>고대 아고라 · 헤파이스토스 신전</t>
         </is>
       </c>
       <c r="C17" s="54" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
@@ -3002,7 +3138,7 @@
       </c>
       <c r="F17" s="47" t="inlineStr">
         <is>
-          <t>hhticket.gr 공식 정가 30유로(연중 동일) · 타임드 엔트리 필수 · 60일 전 오픈, 성수기 5~7일 전 매진</t>
+          <t>통합권 폐지로 별도 구매 필요 — 현장 확인</t>
         </is>
       </c>
     </row>
@@ -3014,11 +3150,11 @@
       </c>
       <c r="B18" s="41" t="inlineStr">
         <is>
-          <t>고대 아고라 · 헤파이스토스 신전</t>
+          <t>아크로폴리스 박물관</t>
         </is>
       </c>
       <c r="C18" s="54" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D18" s="45" t="inlineStr">
         <is>
@@ -3031,36 +3167,36 @@
       </c>
       <c r="F18" s="47" t="inlineStr">
         <is>
-          <t>통합권 폐지로 별도 구매 필요 — 현장 확인</t>
+          <t>실제 확인가 (별도 티켓)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="38">
       <c r="A19" s="45" t="inlineStr">
         <is>
-          <t>10/3</t>
+          <t>10/4</t>
         </is>
       </c>
       <c r="B19" s="41" t="inlineStr">
         <is>
-          <t>아크로폴리스 박물관</t>
+          <t>루브르 아부다비</t>
         </is>
       </c>
       <c r="C19" s="54" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="D19" s="45" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="E19" s="48">
-        <f>ROUND(C19*환율!$B$6,0)</f>
+        <f>ROUND(C19*환율!$B$7,0)</f>
         <v/>
       </c>
       <c r="F19" s="47" t="inlineStr">
         <is>
-          <t>실제 확인가 (별도 티켓)</t>
+          <t>10/4 일요일 10:00~20:30, 최종 입장 20:00 · 월요일 휴관 · 돔은 자정까지</t>
         </is>
       </c>
     </row>
@@ -3072,11 +3208,11 @@
       </c>
       <c r="B20" s="41" t="inlineStr">
         <is>
-          <t>루브르 아부다비</t>
+          <t>셰이크 자이드 그랜드 모스크</t>
         </is>
       </c>
       <c r="C20" s="54" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D20" s="45" t="inlineStr">
         <is>
@@ -3089,52 +3225,52 @@
       </c>
       <c r="F20" s="47" t="inlineStr">
         <is>
-          <t>10/4 일요일 10:00~20:30, 최종 입장 20:00 · 월요일 휴관 · 돔은 자정까지</t>
+          <t>무료</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="38">
       <c r="A21" s="45" t="inlineStr">
         <is>
-          <t>10/4</t>
+          <t>10/2</t>
         </is>
       </c>
       <c r="B21" s="41" t="inlineStr">
         <is>
-          <t>셰이크 자이드 그랜드 모스크</t>
+          <t>마테나다란 고문서관</t>
         </is>
       </c>
       <c r="C21" s="54" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="D21" s="45" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="E21" s="48">
-        <f>ROUND(C21*환율!$B$7,0)</f>
+        <f>ROUND(C21*환율!$B$5,0)</f>
         <v/>
       </c>
       <c r="F21" s="47" t="inlineStr">
         <is>
-          <t>무료</t>
+          <t>화~토 10:00~17:50 · 금요일 개관</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="38">
       <c r="A22" s="45" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>10/2</t>
         </is>
       </c>
       <c r="B22" s="41" t="inlineStr">
         <is>
-          <t>지토그흐치안 도시생활박물관 (귬리)</t>
+          <t>카페시안 미술관</t>
         </is>
       </c>
       <c r="C22" s="54" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D22" s="45" t="inlineStr">
         <is>
@@ -3147,23 +3283,23 @@
       </c>
       <c r="F22" s="47" t="inlineStr">
         <is>
-          <t>화~금 10:00~17:00 · 일요일 개관 여부 현지 확인</t>
+          <t>기부제 · 금~일 20:00까지</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="38">
       <c r="A23" s="45" t="inlineStr">
         <is>
-          <t>10/2</t>
+          <t>10/1</t>
         </is>
       </c>
       <c r="B23" s="41" t="inlineStr">
         <is>
-          <t>마테나다란 고문서관</t>
+          <t>성 흐립시메 교회</t>
         </is>
       </c>
       <c r="C23" s="54" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="D23" s="45" t="inlineStr">
         <is>
@@ -3176,23 +3312,23 @@
       </c>
       <c r="F23" s="47" t="inlineStr">
         <is>
-          <t>화~토 10:00~17:50 · 금요일 개관</t>
+          <t>무료 · 유네스코</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="38">
       <c r="A24" s="45" t="inlineStr">
         <is>
-          <t>10/2</t>
+          <t>10/1</t>
         </is>
       </c>
       <c r="B24" s="41" t="inlineStr">
         <is>
-          <t>카페시안 미술관</t>
+          <t>즈바르트노츠 유적</t>
         </is>
       </c>
       <c r="C24" s="54" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="D24" s="45" t="inlineStr">
         <is>
@@ -3205,7 +3341,7 @@
       </c>
       <c r="F24" s="47" t="inlineStr">
         <is>
-          <t>기부제 · 금~일 20:00까지</t>
+          <t>7세기 원형 성당 터</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3353,7 @@
       </c>
       <c r="B25" s="41" t="inlineStr">
         <is>
-          <t>성 흐립시메 교회</t>
+          <t>대학살 추모관 박물관</t>
         </is>
       </c>
       <c r="C25" s="54" t="n">
@@ -3234,23 +3370,23 @@
       </c>
       <c r="F25" s="47" t="inlineStr">
         <is>
-          <t>무료 · 유네스코</t>
+          <t>무료 · 17:00 마감 · 월요일 휴관</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="38">
       <c r="A26" s="45" t="inlineStr">
         <is>
-          <t>10/1</t>
+          <t>9/29</t>
         </is>
       </c>
       <c r="B26" s="41" t="inlineStr">
         <is>
-          <t>즈바르트노츠 유적</t>
+          <t>노라방크</t>
         </is>
       </c>
       <c r="C26" s="54" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="D26" s="45" t="inlineStr">
         <is>
@@ -3263,19 +3399,19 @@
       </c>
       <c r="F26" s="47" t="inlineStr">
         <is>
-          <t>7세기 원형 성당 터</t>
+          <t>무료 · 투어 포함</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="38">
       <c r="A27" s="45" t="inlineStr">
         <is>
-          <t>10/1</t>
+          <t>9/29</t>
         </is>
       </c>
       <c r="B27" s="41" t="inlineStr">
         <is>
-          <t>대학살 추모관 박물관</t>
+          <t>윙스 오브 타테브 케이블카</t>
         </is>
       </c>
       <c r="C27" s="54" t="n">
@@ -3292,7 +3428,7 @@
       </c>
       <c r="F27" s="47" t="inlineStr">
         <is>
-          <t>무료 · 17:00 마감 · 월요일 휴관</t>
+          <t>투어 요금에 포함 (개별 구매 시 8,000드람) · 월요일 휴무</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3440,7 @@
       </c>
       <c r="B28" s="41" t="inlineStr">
         <is>
-          <t>노라방크</t>
+          <t>타테브 수도원</t>
         </is>
       </c>
       <c r="C28" s="54" t="n">
@@ -3321,65 +3457,65 @@
       </c>
       <c r="F28" s="47" t="inlineStr">
         <is>
-          <t>무료 · 투어 포함</t>
+          <t>무료</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="45" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>9/25</t>
         </is>
       </c>
       <c r="B29" s="41" t="inlineStr">
         <is>
-          <t>윙스 오브 타테브 케이블카</t>
+          <t>다디아니 궁전 박물관</t>
         </is>
       </c>
       <c r="C29" s="54" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D29" s="45" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="E29" s="48">
-        <f>ROUND(C29*환율!$B$5,0)</f>
+        <f>ROUND(C29*환율!$B$4,0)</f>
         <v/>
       </c>
       <c r="F29" s="47" t="inlineStr">
         <is>
-          <t>투어 요금에 포함 (개별 구매 시 8,000드람) · 월요일 휴무</t>
+          <t>화~일 10:00~18:00, 월요일 휴관 · 자료마다 12~15라리로 다름</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="45" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>9/25</t>
         </is>
       </c>
       <c r="B30" s="41" t="inlineStr">
         <is>
-          <t>타테브 수도원</t>
+          <t>다디아니 식물원</t>
         </is>
       </c>
       <c r="C30" s="54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D30" s="45" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="E30" s="48">
-        <f>ROUND(C30*환율!$B$5,0)</f>
+        <f>ROUND(C30*환율!$B$4,0)</f>
         <v/>
       </c>
       <c r="F30" s="47" t="inlineStr">
         <is>
-          <t>무료</t>
+          <t>매일 10:00~18:00</t>
         </is>
       </c>
     </row>
@@ -3533,11 +3669,11 @@
         <v>6000</v>
       </c>
       <c r="H5" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A5,교통상세!$D$5:$D$38,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A5,교통상세!$D$5:$D$41,"시외")</f>
         <v/>
       </c>
       <c r="I5" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A5,교통상세!$D$5:$D$38,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A5,교통상세!$D$5:$D$41,"시내")</f>
         <v/>
       </c>
       <c r="J5" s="48">
@@ -3579,11 +3715,11 @@
         <v>0</v>
       </c>
       <c r="H6" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A6,교통상세!$D$5:$D$38,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A6,교통상세!$D$5:$D$41,"시외")</f>
         <v/>
       </c>
       <c r="I6" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A6,교통상세!$D$5:$D$38,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A6,교통상세!$D$5:$D$41,"시내")</f>
         <v/>
       </c>
       <c r="J6" s="48">
@@ -3625,11 +3761,11 @@
         <v>6000</v>
       </c>
       <c r="H7" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A7,교통상세!$D$5:$D$38,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A7,교통상세!$D$5:$D$41,"시외")</f>
         <v/>
       </c>
       <c r="I7" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A7,교통상세!$D$5:$D$38,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A7,교통상세!$D$5:$D$41,"시내")</f>
         <v/>
       </c>
       <c r="J7" s="48">
@@ -3671,11 +3807,11 @@
         <v>6000</v>
       </c>
       <c r="H8" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A8,교통상세!$D$5:$D$38,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A8,교통상세!$D$5:$D$41,"시외")</f>
         <v/>
       </c>
       <c r="I8" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A8,교통상세!$D$5:$D$38,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A8,교통상세!$D$5:$D$41,"시내")</f>
         <v/>
       </c>
       <c r="J8" s="48">
@@ -3717,11 +3853,11 @@
         <v>5000</v>
       </c>
       <c r="H9" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A9,교통상세!$D$5:$D$38,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A9,교통상세!$D$5:$D$41,"시외")</f>
         <v/>
       </c>
       <c r="I9" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A9,교통상세!$D$5:$D$38,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A9,교통상세!$D$5:$D$41,"시내")</f>
         <v/>
       </c>
       <c r="J9" s="48">
@@ -3746,7 +3882,7 @@
       </c>
       <c r="C10" s="64" t="inlineStr">
         <is>
-          <t>주타 데이 트레킹 → 트빌리시 복귀</t>
+          <t>주타 데이 트레킹(쉬운 코스) → 트빌리시 복귀 → 야간버스로 주그디디행</t>
         </is>
       </c>
       <c r="D10" s="54">
@@ -3757,17 +3893,17 @@
         <v>25000</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>15689</v>
+        <v>0</v>
       </c>
       <c r="G10" s="54" t="n">
         <v>5000</v>
       </c>
       <c r="H10" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A10,교통상세!$D$5:$D$38,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A10,교통상세!$D$5:$D$41,"시외")</f>
         <v/>
       </c>
       <c r="I10" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A10,교통상세!$D$5:$D$38,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A10,교통상세!$D$5:$D$41,"시내")</f>
         <v/>
       </c>
       <c r="J10" s="48">
@@ -3792,7 +3928,7 @@
       </c>
       <c r="C11" s="64" t="inlineStr">
         <is>
-          <t>시그나기 · 보드베 당일치기 (카헤티)</t>
+          <t>주그디디 도착 → 다디아니 궁전·식물원 → 메스티아 이동·체크인</t>
         </is>
       </c>
       <c r="D11" s="54">
@@ -3803,17 +3939,17 @@
         <v>25000</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>15689</v>
+        <v>25000</v>
       </c>
       <c r="G11" s="54" t="n">
         <v>5000</v>
       </c>
       <c r="H11" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A11,교통상세!$D$5:$D$38,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A11,교통상세!$D$5:$D$41,"시외")</f>
         <v/>
       </c>
       <c r="I11" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A11,교통상세!$D$5:$D$38,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A11,교통상세!$D$5:$D$41,"시내")</f>
         <v/>
       </c>
       <c r="J11" s="48">
@@ -3838,7 +3974,7 @@
       </c>
       <c r="C12" s="66" t="inlineStr">
         <is>
-          <t>알라베르디 — 하흐파트·사나힌</t>
+          <t>메스티아 찰라디 빙하 트레킹 → 주그디디 → 야간버스로 트빌리시행</t>
         </is>
       </c>
       <c r="D12" s="54">
@@ -3849,17 +3985,17 @@
         <v>25000</v>
       </c>
       <c r="F12" s="54" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="G12" s="54" t="n">
         <v>5000</v>
       </c>
       <c r="H12" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A12,교통상세!$D$5:$D$38,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A12,교통상세!$D$5:$D$41,"시외")</f>
         <v/>
       </c>
       <c r="I12" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A12,교통상세!$D$5:$D$38,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A12,교통상세!$D$5:$D$41,"시내")</f>
         <v/>
       </c>
       <c r="J12" s="48">
@@ -3884,7 +4020,7 @@
       </c>
       <c r="C13" s="66" t="inlineStr">
         <is>
-          <t>귬리 — 쿠마이리 구시가</t>
+          <t>야간버스로 트빌리시 도착 → 국경 → 알라베르디(하흐파트·사나힌)</t>
         </is>
       </c>
       <c r="D13" s="54">
@@ -3892,20 +4028,20 @@
         <v/>
       </c>
       <c r="E13" s="54" t="n">
-        <v>27000</v>
+        <v>25000</v>
       </c>
       <c r="F13" s="54" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="G13" s="54" t="n">
         <v>5000</v>
       </c>
       <c r="H13" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A13,교통상세!$D$5:$D$38,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A13,교통상세!$D$5:$D$41,"시외")</f>
         <v/>
       </c>
       <c r="I13" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A13,교통상세!$D$5:$D$38,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A13,교통상세!$D$5:$D$41,"시내")</f>
         <v/>
       </c>
       <c r="J13" s="48">
@@ -3930,7 +4066,7 @@
       </c>
       <c r="C14" s="66" t="inlineStr">
         <is>
-          <t>예레반 — 귬리에서 이동 · 시내</t>
+          <t>알라베르디 → 바나조르 환승 → 예레반 도착 · 시내(GUM·블루모스크·캐스케이드)</t>
         </is>
       </c>
       <c r="D14" s="54">
@@ -3947,11 +4083,11 @@
         <v>6000</v>
       </c>
       <c r="H14" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A14,교통상세!$D$5:$D$38,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A14,교통상세!$D$5:$D$41,"시외")</f>
         <v/>
       </c>
       <c r="I14" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A14,교통상세!$D$5:$D$38,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A14,교통상세!$D$5:$D$41,"시내")</f>
         <v/>
       </c>
       <c r="J14" s="48">
@@ -3993,11 +4129,11 @@
         <v>6000</v>
       </c>
       <c r="H15" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A15,교통상세!$D$5:$D$38,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A15,교통상세!$D$5:$D$41,"시외")</f>
         <v/>
       </c>
       <c r="I15" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A15,교통상세!$D$5:$D$38,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A15,교통상세!$D$5:$D$41,"시내")</f>
         <v/>
       </c>
       <c r="J15" s="48">
@@ -4039,11 +4175,11 @@
         <v>5000</v>
       </c>
       <c r="H16" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A16,교통상세!$D$5:$D$38,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A16,교통상세!$D$5:$D$41,"시외")</f>
         <v/>
       </c>
       <c r="I16" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A16,교통상세!$D$5:$D$38,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A16,교통상세!$D$5:$D$41,"시내")</f>
         <v/>
       </c>
       <c r="J16" s="48">
@@ -4085,11 +4221,11 @@
         <v>5000</v>
       </c>
       <c r="H17" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A17,교통상세!$D$5:$D$38,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A17,교통상세!$D$5:$D$41,"시외")</f>
         <v/>
       </c>
       <c r="I17" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A17,교통상세!$D$5:$D$38,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A17,교통상세!$D$5:$D$41,"시내")</f>
         <v/>
       </c>
       <c r="J17" s="48">
@@ -4131,11 +4267,11 @@
         <v>6000</v>
       </c>
       <c r="H18" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A18,교통상세!$D$5:$D$38,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A18,교통상세!$D$5:$D$41,"시외")</f>
         <v/>
       </c>
       <c r="I18" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A18,교통상세!$D$5:$D$38,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A18,교통상세!$D$5:$D$41,"시내")</f>
         <v/>
       </c>
       <c r="J18" s="48">
@@ -4177,11 +4313,11 @@
         <v>8000</v>
       </c>
       <c r="H19" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A19,교통상세!$D$5:$D$38,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A19,교통상세!$D$5:$D$41,"시외")</f>
         <v/>
       </c>
       <c r="I19" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A19,교통상세!$D$5:$D$38,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A19,교통상세!$D$5:$D$41,"시내")</f>
         <v/>
       </c>
       <c r="J19" s="48">
@@ -4223,11 +4359,11 @@
         <v>8000</v>
       </c>
       <c r="H20" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A20,교통상세!$D$5:$D$38,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A20,교통상세!$D$5:$D$41,"시외")</f>
         <v/>
       </c>
       <c r="I20" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A20,교통상세!$D$5:$D$38,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A20,교통상세!$D$5:$D$41,"시내")</f>
         <v/>
       </c>
       <c r="J20" s="48">
@@ -4269,11 +4405,11 @@
         <v>0</v>
       </c>
       <c r="H21" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A21,교통상세!$D$5:$D$38,"시외")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A21,교통상세!$D$5:$D$41,"시외")</f>
         <v/>
       </c>
       <c r="I21" s="54">
-        <f>SUMIFS(교통상세!$G$5:$G$38,교통상세!$A$5:$A$38,A21,교통상세!$D$5:$D$38,"시내")</f>
+        <f>SUMIFS(교통상세!$G$5:$G$41,교통상세!$A$5:$A$41,A21,교통상세!$D$5:$D$41,"시내")</f>
         <v/>
       </c>
       <c r="J21" s="48">
@@ -4397,14 +4533,14 @@
     <row r="32" ht="15" customHeight="1" s="38">
       <c r="A32" s="49" t="inlineStr">
         <is>
-          <t>※ 확정 숙소 — 상하이 Hi Cozy International Youth Hostel 137위안/1박(황푸구, 난징둥루역 도보권), 트빌리시 Cosy Koala Hostel 58라리/2박. 트빌리시는 9/22·9/25 두 밤이 추가로 필요합니다.</t>
+          <t>※ 확정 숙소 — 상하이 Hi Cozy International Youth Hostel 137위안/1박(황푸구, 난징둥루역 도보권), 트빌리시 Cosy Koala Hostel 58라리 — 9/20~22 3박만 연속으로 예약하면 됩니다. 9/24·9/26 밤은 야간버스, 9/27은 몇 시간만 머물다 알라베르디로 넘어가는 날이라 트빌리시 추가 숙박은 필요 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="38">
       <c r="A33" s="50" t="inlineStr">
         <is>
-          <t>※ 미예약 숙소(카즈베기·알라베르디·딜리잔·예레반·고리스)는 도미토리 기준 추정치입니다. 개인실을 잡으면 1인 여행이라 이 금액의 두 배 가까이 올라갑니다.</t>
+          <t>※ 미예약 숙소(카즈베기·메스티아·알라베르디·예레반)는 도미토리 기준 추정치입니다. 개인실을 잡으면 1인 여행이라 이 금액의 두 배 가까이 올라갑니다.</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4565,13 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>※ 9/26 메스티아→트레일헤드 택시 왕복 50라리는 조지아 구간에서 주타 다음으로 큰 단일 지출입니다. 동행을 구하면 반값이 됩니다.</t>
+        </is>
+      </c>
+    </row>
     <row r="38"/>
     <row r="39"/>
     <row r="40"/>
